--- a/data/credit_bond_all_2026-09-04.xlsx
+++ b/data/credit_bond_all_2026-09-04.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-04" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-04</t>
+          <t>数据来源：DM    2026-09-07</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -719,8 +719,12 @@
           <t>2.00 ~ 3.00</t>
         </is>
       </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3"/>
+      <c r="H3" s="4" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>75.86</v>
+      </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
           <t>2.32</t>
@@ -738,7 +742,7 @@
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.1684</t>
+          <t>2.1600</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
@@ -753,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 17.40</t>
+          <t>C- 16.50</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -968,12 +972,12 @@
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.9334</t>
+          <t>1.9285</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t>--/1.8600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
@@ -1141,7 +1145,9 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ4" s="3"/>
+      <c r="AZ4" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
@@ -1167,7 +1173,9 @@
       <c r="E5" s="4" t="n">
         <v>5.0</v>
       </c>
-      <c r="F5" s="3"/>
+      <c r="F5" s="4" t="n">
+        <v>5.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 1.80</t>
@@ -1192,12 +1200,12 @@
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.5408</t>
+          <t>1.5483</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1395,7 +1403,9 @@
       <c r="E6" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F6" s="3"/>
+      <c r="F6" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
           <t>1.30 ~ 2.10</t>
@@ -1425,7 +1435,7 @@
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.6400/1.6000</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
@@ -1435,7 +1445,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 36.92</t>
+          <t>B- 39.23</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1621,7 +1631,9 @@
       <c r="E7" s="4" t="n">
         <v>4.0</v>
       </c>
-      <c r="F7" s="3"/>
+      <c r="F7" s="4" t="n">
+        <v>4.0</v>
+      </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
           <t>1.35 ~ 1.55</t>
@@ -1651,7 +1663,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>1.5800/1.4296</t>
+          <t>--/1.4296</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
@@ -1824,68 +1836,70 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26余产K2</t>
+          <t>26国泰海通CP007</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>520462.SZ</t>
+          <t>072610176.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
-      <c r="H8" s="3"/>
-      <c r="I8" s="3"/>
+        <v>40.0</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>28.27</v>
+      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26余产K1</t>
+          <t>26国泰海通CP003</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>2.51Y+2.00Y</t>
+          <t>217D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.7708</t>
+          <t>1.4741</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.8000/--</t>
+          <t>1.5000/1.4600</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭产业投资发展有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>B+ 58.17</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1895,7 +1909,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1905,19 +1919,19 @@
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U8" s="3"/>
       <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1928,23 +1942,19 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
-        </is>
-      </c>
-      <c r="AB8" s="3" t="inlineStr">
-        <is>
-          <t>本期债券募集资金扣除发行费用后全部用于科技创新领域的股权投资和基金出资,包含置换前期出资和新增出资等,置换后的资金将用于符合国家宏观调控和产业政策要求的用途,不直接或者间接用于缴纳土地出让金。发行人拟将本期债券募集资金全部用于置换前期出资的基金或投资项目,其中拟用于置换基金出资33,700万元,拟用于置换股权直投项目出资16,300万元,总金额不超过5.00亿元。[杭州君联良道股权投资合伙企业(有限合伙),浙江千帆企航贰号股权投资基金合伙企业(有限合伙),杭州元璟新创中小创业投资合伙企业(有限合伙),杭州杭实低空产业私募基金合伙企业(有限合伙),钛虎机器人科技(上海)有限公司,杭州佳量脑科学股份有限公司,灵伴科技(杭州)股份有限公司]</t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB8" s="3"/>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,财通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
@@ -1954,68 +1964,68 @@
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭产业投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2048,17 +2058,17 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26淳安02</t>
+          <t>26浔旅02</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 17:30</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>283908.SH</t>
+          <t>283906.SH</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -2067,49 +2077,53 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>6.5</v>
+        <v>5.6</v>
       </c>
       <c r="F9" s="3"/>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
-        </is>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>78.86</v>
+      </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>26淳安01</t>
+          <t>24浔旅03</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>3.02Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.9527</t>
+          <t>1.9196</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司</t>
+          <t>湖州南浔文旅发展集团有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.50</t>
+          <t>C 29.81</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2129,14 +2143,14 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U9" s="3"/>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>7</t>
         </is>
       </c>
       <c r="X9" s="3"/>
@@ -2148,17 +2162,17 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
+          <t>本期债券为上述无异议函下第二期发行,发行金额为不超过5.60亿元(含),发行后募集资金将用于偿还到期的公司债券本金。[23浔旅02]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>财通证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
@@ -2179,7 +2193,7 @@
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>湖州南浔文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
@@ -2189,14 +2203,10 @@
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK9" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2209,37 +2219,37 @@
       </c>
       <c r="AN9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2272,17 +2282,17 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26浔旅02</t>
+          <t>26淳安02</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>283906.SH</t>
+          <t>283908.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
@@ -2291,49 +2301,53 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>5.6</v>
+        <v>6.5</v>
       </c>
       <c r="F10" s="3"/>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
-        </is>
-      </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+          <t>1.50 ~ 2.50</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>66.86</v>
+      </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>24浔旅03</t>
+          <t>26淳安01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>3.02Y</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.9214</t>
+          <t>1.9466</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/1.8400</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>湖州南浔文旅发展集团有限公司</t>
+          <t>淳安县国有资产投资集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C 29.81</t>
+          <t>D+ 6.50</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2353,14 +2367,14 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U10" s="3"/>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X10" s="3"/>
@@ -2372,17 +2386,17 @@
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券为上述无异议函下第二期发行,发行金额为不超过5.60亿元(含),发行后募集资金将用于偿还到期的公司债券本金。[23浔旅02]</t>
+          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,德邦证券股份有限公司</t>
+          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
@@ -2403,7 +2417,7 @@
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>湖州南浔文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
@@ -2413,10 +2427,14 @@
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK10" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK10" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL10" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2429,37 +2447,25 @@
       </c>
       <c r="AN10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP10" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR10" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS10" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ10" s="3"/>
+      <c r="AR10" s="3"/>
+      <c r="AS10" s="3"/>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2492,66 +2498,72 @@
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP007</t>
+          <t>26清浦02</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>072610176.IB</t>
+          <t>283882.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>40.0</v>
+        <v>1.5</v>
       </c>
       <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>1.80 ~ 2.80</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="I11" s="3"/>
+        <v>2.12</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>71.86</v>
+      </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP003</t>
+          <t>26清浦01</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>217D</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.4741</t>
+          <t>2.1514</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4700</t>
+          <t>2.1800/2.1600</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>淮安市清江浦融合投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.43</t>
+          <t>C+ 30.21</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2561,7 +2573,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2578,35 +2590,35 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X11" s="3" t="inlineStr">
-        <is>
-          <t>1.47%~1.51%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X11" s="3"/>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB11" s="3"/>
+          <t>江苏省-淮安市</t>
+        </is>
+      </c>
+      <c r="AB11" s="3" t="inlineStr">
+        <is>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还存量公司债券到期本金[23清浦03]</t>
+        </is>
+      </c>
       <c r="AC11" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>天风证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
@@ -2616,28 +2628,32 @@
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
+          <t>淮安市清江浦融合投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
-        </is>
-      </c>
-      <c r="AK11" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK11" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2652,32 +2668,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>7.5*无效</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2710,17 +2726,17 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26古都01</t>
+          <t>26余产K2</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>283920.SH</t>
+          <t>520462.SZ</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2729,49 +2745,53 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
       <c r="F12" s="3"/>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
-        </is>
-      </c>
-      <c r="H12" s="3"/>
-      <c r="I12" s="3"/>
+          <t>1.40 ~ 2.40</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>54.86</v>
+      </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24古都01</t>
+          <t>26余产K1</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>358D</t>
+          <t>2.51Y+2.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.3779</t>
+          <t>1.7654</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/2.3500</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>洛阳古都发展集团有限公司</t>
+          <t>杭州余杭产业投资发展有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>B- 47.00</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2791,43 +2811,43 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U12" s="3"/>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X12" s="3"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X12" s="3" t="inlineStr">
+        <is>
+          <t>1.85%~1.95%</t>
+        </is>
+      </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>河南省-洛阳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金不超过3亿元(含3亿元)。本次债券募集资金扣除发行费用后拟全部用于偿还“23古都01”债券本金。[23 古都01]</t>
+          <t>本期债券募集资金扣除发行费用后全部用于科技创新领域的股权投资和基金出资,包含置换前期出资和新增出资等,置换后的资金将用于符合国家宏观调控和产业政策要求的用途,不直接或者间接用于缴纳土地出让金。发行人拟将本期债券募集资金全部用于置换前期出资的基金或投资项目,其中拟用于置换基金出资33,700万元,拟用于置换股权直投项目出资16,300万元,总金额不超过5.00亿元。[杭州君联良道股权投资合伙企业(有限合伙),浙江千帆企航贰号股权投资基金合伙企业(有限合伙),杭州元璟新创中小创业投资合伙企业(有限合伙),杭州杭实低空产业私募基金合伙企业(有限合伙),钛虎机器人科技(上海)有限公司,杭州佳量脑科学股份有限公司,灵伴科技(杭州)股份有限公司]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中原证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>河南省中豫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>华泰联合证券有限责任公司,财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2840,12 +2860,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>洛阳古都发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>杭州余杭产业投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2855,14 +2875,10 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK12" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2870,22 +2886,22 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2905,7 +2921,7 @@
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2915,7 +2931,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -2938,60 +2954,72 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债02</t>
+          <t>26山钢Y7</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
-        </is>
-      </c>
-      <c r="C13" s="3"/>
+          <t>09-04 19:00</t>
+        </is>
+      </c>
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>283876.SH</t>
+        </is>
+      </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>100.0</v>
+        <v>9.0</v>
       </c>
       <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>74.22</v>
+      </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债01BC</t>
+          <t>26山钢Y6</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.5714</t>
+          <t>2.0599</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>1.5720/1.5720</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司</t>
+          <t>山东钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>S 91.50</t>
+          <t>B- 38.49</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3001,7 +3029,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:30</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3018,12 +3046,12 @@
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.64%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
@@ -3034,39 +3062,43 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC13" s="3"/>
+          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+        </is>
+      </c>
+      <c r="AC13" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
+        </is>
+      </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司2026年金融债券(第二期)</t>
+          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
@@ -3092,32 +3124,32 @@
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ13" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR13" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
@@ -3132,12 +3164,12 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY13" s="3" t="inlineStr">
@@ -3150,53 +3182,57 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26国新保理SCP007</t>
+          <t>26古都01</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>012682208.IB</t>
+          <t>283920.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.52</t>
-        </is>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
+          <t>2.30 ~ 3.30</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>89.86</v>
+      </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>25国保01</t>
+          <t>24古都01</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>293D</t>
+          <t>358D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.5453</t>
+          <t>2.3885</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3206,12 +3242,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司</t>
+          <t>洛阳古都发展集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>C 26.74</t>
+          <t>A 80.00</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3221,7 +3257,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3238,75 +3274,79 @@
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>1.52%~1.56%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X14" s="3"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>河南省-洛阳市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>发行人注册80亿元超短期融资券,本次发行10亿元,拟用于偿还有息负债[25国新保理SCP006]</t>
+          <t>本次债券募集资金不超过3亿元(含3亿元)。本次债券募集资金扣除发行费用后拟全部用于偿还“23古都01”债券本金。[23 古都01]</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3"/>
+          <t>中原证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3" t="inlineStr">
+        <is>
+          <t>河南省中豫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司2026年度第七期超短期融资券</t>
+          <t>洛阳古都发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3316,28 +3356,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP14" s="3"/>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP14" s="3" t="inlineStr">
+        <is>
+          <t>8.5</t>
+        </is>
+      </c>
       <c r="AQ14" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR14" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3347,7 +3391,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3365,24 +3409,22 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ14" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ14" s="3"/>
     </row>
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26中海油租MTN001</t>
+          <t>26广发银行债02</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683538.IB</t>
+          <t>212680036.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
@@ -3391,49 +3433,51 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3" t="inlineStr">
-        <is>
-          <t>1.54 ~ 1.74</t>
-        </is>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
+        <v>100.0</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="G15" s="3"/>
+      <c r="H15" s="4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>32.22</v>
+      </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>25中海油租MTN002(绿色)</t>
+          <t>26广发银行债01BC</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>1.05Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5561</t>
+          <t>1.5714</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5750/1.5700</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司</t>
+          <t>广发银行股份有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>B 54.00</t>
+          <t>S 91.50</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3443,7 +3487,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 09:30</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3460,12 +3504,12 @@
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.54%~1.64%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3476,23 +3520,19 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
-        </is>
-      </c>
-      <c r="AC15" s="3" t="inlineStr">
-        <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC15" s="3"/>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3507,7 +3547,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
+          <t>广发银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3523,7 +3563,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3543,27 +3583,27 @@
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3596,7 +3636,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>26国新保理SCP007</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3606,58 +3646,60 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683536.IB</t>
+          <t>012682208.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
         <v>10.0</v>
       </c>
-      <c r="F16" s="3"/>
+      <c r="F16" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.98</t>
+          <t>1.32 ~ 1.52</t>
         </is>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN014</t>
+          <t>25国保01</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>293D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.0055</t>
+          <t>1.5446</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>2.0000/2.0000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>国新商业保理有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 40.75</t>
+          <t>C 25.66</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3684,12 +3726,12 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.52%~1.56%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3700,28 +3742,28 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t>发行人注册80亿元超短期融资券,本次发行10亿元,拟用于偿还有息负债[25国新保理SCP006]</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3731,7 +3773,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
+          <t>国新商业保理有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3741,14 +3783,10 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-04</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -3766,32 +3804,28 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>保理</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3819,12 +3853,14 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y7</t>
+          <t>26中海油租MTN001</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3834,58 +3870,60 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283876.SH</t>
+          <t>102683538.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="F17" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.54 ~ 1.74</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y6</t>
+          <t>25中海油租MTN002(绿色)</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>1.05Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.0528</t>
+          <t>1.5561</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>2.0800/--</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司</t>
+          <t>中海油国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 39.81</t>
+          <t>B 54.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3895,7 +3933,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3917,7 +3955,7 @@
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -3928,43 +3966,43 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
+          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
@@ -3975,54 +4013,54 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4030,12 +4068,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4043,22 +4081,24 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26清浦02</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>283882.SH</t>
+          <t>102683536.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
@@ -4067,49 +4107,51 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F18" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.50 ~ 1.98</t>
         </is>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26清浦01</t>
+          <t>26晋能煤业MTN014</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.1489</t>
+          <t>2.0055</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2.1800/2.1600</t>
+          <t>2.0000/1.9900</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>淮安市清江浦融合投资控股集团有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.21</t>
+          <t>B- 39.54</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4119,7 +4161,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4136,35 +4178,39 @@
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X18" s="3"/>
+          <t>6-</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.92%~2.02%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还存量公司债券到期本金[23清浦03]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,财通证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4174,17 +4220,17 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>淮安市清江浦融合投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
@@ -4199,7 +4245,7 @@
       </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
@@ -4214,32 +4260,32 @@
       </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>7.5*无效</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4277,7 +4323,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -4299,11 +4345,15 @@
           <t>1.50 ~ 2.30</t>
         </is>
       </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
+      <c r="H19" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>13.96</v>
+      </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
@@ -4318,7 +4368,7 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.8196</t>
+          <t>1.8095</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4333,7 +4383,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 35.16</t>
+          <t>C+ 33.08</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4442,21 +4492,9 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
+      <c r="AQ19" s="3"/>
+      <c r="AR19" s="3"/>
+      <c r="AS19" s="3"/>
       <c r="AT19" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>

--- a/data/credit_bond_all_2026-09-04.xlsx
+++ b/data/credit_bond_all_2026-09-04.xlsx
@@ -953,8 +953,12 @@
           <t>1.50 ~ 2.00</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>76.34</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>2.00</t>
@@ -1006,7 +1010,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -1205,7 +1211,7 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5500/--</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
@@ -1411,8 +1417,12 @@
           <t>1.30 ~ 2.10</t>
         </is>
       </c>
-      <c r="H6" s="3"/>
-      <c r="I6" s="3"/>
+      <c r="H6" s="4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>44.22</v>
+      </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
           <t>1.74</t>
@@ -1468,7 +1478,9 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U6" s="3"/>
+      <c r="U6" s="4" t="n">
+        <v>4.92</v>
+      </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
@@ -1603,9 +1615,7 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ6" s="4" t="n">
-        <v>0.02</v>
-      </c>
+      <c r="AZ6" s="3"/>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
@@ -1639,8 +1649,12 @@
           <t>1.35 ~ 1.55</t>
         </is>
       </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3"/>
+      <c r="H7" s="4" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>21.84</v>
+      </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
           <t>1.50</t>
@@ -3665,8 +3679,12 @@
           <t>1.32 ~ 1.52</t>
         </is>
       </c>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
+      <c r="H16" s="4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>32.84</v>
+      </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3860,7 +3878,7 @@
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26中海油租MTN001</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3870,12 +3888,12 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683538.IB</t>
+          <t>102683536.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -3886,44 +3904,44 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.54 ~ 1.74</t>
+          <t>1.50 ~ 1.98</t>
         </is>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>25中海油租MTN002(绿色)</t>
+          <t>26晋能煤业MTN014</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>1.05Y</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.5561</t>
+          <t>2.0055</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/1.9900</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B 54.00</t>
+          <t>B- 39.54</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3950,12 +3968,12 @@
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -3966,17 +3984,17 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
@@ -3987,7 +4005,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -3997,7 +4015,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
+          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4007,10 +4025,14 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK17" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK17" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -4028,32 +4050,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4081,77 +4103,77 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.01</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>26古厝12</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683536.IB</t>
+          <t>246004.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>10.0</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>10.0</v>
-      </c>
+        <v>6.8</v>
+      </c>
+      <c r="F18" s="3"/>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.98</t>
-        </is>
-      </c>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
+          <t>1.50 ~ 2.30</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>13.96</v>
+      </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN014</t>
+          <t>26古厝11</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>4.94Y+5.00Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.0055</t>
+          <t>1.8095</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2.0000/1.9900</t>
+          <t>1.8300/1.8100</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 39.54</t>
+          <t>C+ 33.08</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4161,7 +4183,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4171,21 +4193,19 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U18" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="n">
+        <v>4.15</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t>1.92%~2.02%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X18" s="3"/>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4194,23 +4214,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t>本期债券发行金额为不超过人民币6.80亿元(含6.80亿元)。本期债券的募集资金扣除相关发行费用后,拟全部用于偿还到期债务。[25古厝01,23古厝04,25古厝D6,24福州古厝MTN005,25福州古厝MTN003,23福州古厝MTN001]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,天风证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4220,12 +4240,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4235,32 +4255,28 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-09-08</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
@@ -4268,29 +4284,17 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
+      <c r="AQ18" s="3"/>
+      <c r="AR18" s="3"/>
+      <c r="AS18" s="3"/>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AV18" s="3" t="inlineStr">
@@ -4300,7 +4304,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4318,102 +4322,112 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26古厝12</t>
+          <t>26中海油租MTN001</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>246004.SH</t>
+          <t>102683538.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F19" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.54 ~ 1.74</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.82</v>
+        <v>1.69</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>13.96</v>
+        <v>44.22</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>25中海油租MTN002(绿色)</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>1.05Y</t>
+        </is>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>1.5561</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O19" s="3" t="inlineStr">
+        <is>
+          <t>中海油国际融资租赁有限公司</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>B 54.00</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="R19" s="3" t="inlineStr">
+        <is>
+          <t>09-04 09:00</t>
+        </is>
+      </c>
+      <c r="S19" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K19" s="3" t="inlineStr">
-        <is>
-          <t>26古厝11</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr">
-        <is>
-          <t>4.94Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="M19" s="3" t="inlineStr">
-        <is>
-          <t>1.8095</t>
-        </is>
-      </c>
-      <c r="N19" s="3" t="inlineStr">
-        <is>
-          <t>1.8300/1.8100</t>
-        </is>
-      </c>
-      <c r="O19" s="3" t="inlineStr">
-        <is>
-          <t>福州古厝集团有限公司</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.08</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="R19" s="3" t="inlineStr">
-        <is>
-          <t>09-04 15:00</t>
-        </is>
-      </c>
-      <c r="S19" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U19" s="3"/>
-      <c r="V19" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V19" s="4" t="n">
+        <v>1.58</v>
+      </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X19" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X19" s="3" t="inlineStr">
+        <is>
+          <t>1.67%~1.77%</t>
+        </is>
+      </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4422,38 +4436,38 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过人民币6.80亿元(含6.80亿元)。本期债券的募集资金扣除相关发行费用后,拟全部用于偿还到期债务。[25古厝01,23古厝04,25古厝D6,24福州古厝MTN005,25福州古厝MTN003,23福州古厝MTN001]</t>
+          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,天风证券股份有限公司,华福证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4463,48 +4477,60 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2036-09-08</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>融资租赁</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3"/>
-      <c r="AR19" s="3"/>
-      <c r="AS19" s="3"/>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4512,7 +4538,7 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-04.xlsx
+++ b/data/credit_bond_all_2026-09-04.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-07" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-07</t>
+          <t>数据来源：DM    2026-09-08</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 16.50</t>
+          <t>C- 24.77</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -924,59 +924,55 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26腾景科技MTN001(科创债)</t>
+          <t>26东北电力SCP004</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>102683530.IB</t>
+          <t>012682210.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>1.08Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>76.34</v>
-      </c>
+          <t>1.30 ~ 1.80</t>
+        </is>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>23咸金03</t>
+          <t>26东北电力SCP003</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>242D</t>
+          <t>235D</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.9285</t>
+          <t>1.5483</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -986,10 +982,14 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司</t>
-        </is>
-      </c>
-      <c r="P4" s="3"/>
+          <t>国家电投集团东北电力有限公司</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>D+ 7.67</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>2026-09-04</t>
@@ -1007,57 +1007,51 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U4" s="4" t="n">
-        <v>1.0</v>
-      </c>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U4" s="3"/>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
+          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务[26东北电力SCP001]</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD4" s="3" t="inlineStr">
-        <is>
-          <t>福建省融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG4" s="3" t="inlineStr">
@@ -1067,7 +1061,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
+          <t>国家电投集团东北电力有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1077,151 +1071,155 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2027-10-07</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="AK4" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL4" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AM4" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN4" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM4" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN4" s="3" t="inlineStr">
+      <c r="AO4" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP4" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ4" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR4" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS4" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT4" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU4" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV4" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW4" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX4" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY4" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AO4" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP4" s="3"/>
-      <c r="AQ4" s="3" t="inlineStr">
-        <is>
-          <t>电子制造</t>
-        </is>
-      </c>
-      <c r="AR4" s="3" t="inlineStr">
-        <is>
-          <t>电子元器件</t>
-        </is>
-      </c>
-      <c r="AS4" s="3" t="inlineStr">
-        <is>
-          <t>电子元器件</t>
-        </is>
-      </c>
-      <c r="AT4" s="3" t="inlineStr">
-        <is>
-          <t>光学光电子</t>
-        </is>
-      </c>
-      <c r="AU4" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV4" s="3" t="inlineStr">
-        <is>
-          <t>有担保</t>
-        </is>
-      </c>
-      <c r="AW4" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX4" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY4" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="AZ4" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ4" s="3"/>
     </row>
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP004</t>
+          <t>26浔旅02</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-04 17:30</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>012682210.IB</t>
+          <t>283906.SH</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>5.0</v>
-      </c>
+        <v>5.6</v>
+      </c>
+      <c r="F5" s="3"/>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
-        </is>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3"/>
+          <t>1.70 ~ 2.70</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>78.86</v>
+      </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP003</t>
+          <t>24浔旅03</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>235D</t>
+          <t>3.02Y</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.5483</t>
+          <t>1.9196</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>1.5500/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司</t>
+          <t>湖州南浔文旅发展集团有限公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.17</t>
+          <t>C 29.80</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1231,7 +1229,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1248,74 +1246,66 @@
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X5" s="3" t="inlineStr">
-        <is>
-          <t>1.55%~1.59%</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X5" s="3"/>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务[26东北电力SCP001]</t>
+          <t>本期债券为上述无异议函下第二期发行,发行金额为不超过5.60亿元(含),发行后募集资金将用于偿还到期的公司债券本金。[23浔旅02]</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>财通证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司2026年度第四期超短期融资券</t>
+          <t>湖州南浔文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
-        </is>
-      </c>
-      <c r="AK5" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2031-09-08</t>
+        </is>
+      </c>
+      <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t/>
         </is>
       </c>
       <c r="AM5" s="3" t="inlineStr">
@@ -1330,32 +1320,32 @@
       </c>
       <c r="AO5" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP5" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AQ5" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR5" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr">
@@ -1380,7 +1370,7 @@
       </c>
       <c r="AY5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AZ5" s="3"/>
@@ -1388,74 +1378,74 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26淮南矿MTN001</t>
+          <t>26清浦02</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>102683537.IB</t>
+          <t>283882.SH</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>10.0</v>
+        <v>1.5</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.69</v>
+        <v>2.12</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>44.22</v>
+        <v>71.86</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>25淮南矿MTN006</t>
+          <t>26清浦01</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>1.28Y+N</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>1.6292</t>
+          <t>2.1514</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>1.6400/1.6000</t>
+          <t>2.1800/2.1600</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>淮南矿业(集团)有限责任公司</t>
+          <t>淮安市清江浦融合投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>B- 39.23</t>
+          <t>C 27.83</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1465,7 +1455,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1479,44 +1469,40 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>4.92</v>
+        <v>3.07</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X6" s="3" t="inlineStr">
-        <is>
-          <t>1.76%~1.86%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X6" s="3"/>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>安徽省-淮南市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金10亿元，其中5亿元拟用于集团本部及子公司偿还有息债务，5亿元拟用于集团本部及子公司补充营运资金。</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还存量公司债券到期本金[23清浦03]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>天风证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
@@ -1526,28 +1512,32 @@
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>淮南矿业(集团)有限责任公司2026年度第一期中期票据</t>
+          <t>淮安市清江浦融合投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK6" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK6" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM6" s="3" t="inlineStr">
@@ -1562,32 +1552,32 @@
       </c>
       <c r="AO6" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP6" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>7.5*无效</t>
         </is>
       </c>
       <c r="AQ6" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR6" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>城市基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr">
@@ -1602,7 +1592,7 @@
       </c>
       <c r="AW6" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX6" s="3" t="inlineStr">
@@ -1620,74 +1610,72 @@
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP002</t>
+          <t>26余产K2</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>012682209.IB</t>
+          <t>520462.SZ</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>4.0</v>
-      </c>
+        <v>5.0</v>
+      </c>
+      <c r="F7" s="3"/>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H7" s="4" t="n">
-        <v>1.41</v>
+        <v>1.95</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>21.84</v>
+        <v>54.86</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP001</t>
+          <t>26余产K1</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>266D</t>
+          <t>2.51Y+2.00Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.5500</t>
+          <t>1.7654</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/1.4296</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>杭州余杭产业投资发展有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>B 55.00</t>
+          <t>D 5.00</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1697,7 +1685,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1707,19 +1695,19 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.40%~1.44%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1730,94 +1718,94 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金。</t>
+          <t>本期债券募集资金扣除发行费用后全部用于科技创新领域的股权投资和基金出资,包含置换前期出资和新增出资等,置换后的资金将用于符合国家宏观调控和产业政策要求的用途,不直接或者间接用于缴纳土地出让金。发行人拟将本期债券募集资金全部用于置换前期出资的基金或投资项目,其中拟用于置换基金出资33,700万元,拟用于置换股权直投项目出资16,300万元,总金额不超过5.00亿元。[杭州君联良道股权投资合伙企业(有限合伙),浙江千帆企航贰号股权投资基金合伙企业(有限合伙),杭州元璟新创中小创业投资合伙企业(有限合伙),杭州杭实低空产业私募基金合伙企业(有限合伙),钛虎机器人科技(上海)有限公司,杭州佳量脑科学股份有限公司,灵伴科技(杭州)股份有限公司]</t>
         </is>
       </c>
       <c r="AC7" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第二期超短期融资券</t>
+          <t>杭州余杭产业投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM7" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN7" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN7" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1850,70 +1838,74 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP007</t>
+          <t>26中海油租MTN001</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>072610176.IB</t>
+          <t>102683538.IB</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>40.0</v>
+        <v>10.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G8" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>1.54 ~ 1.74</t>
+        </is>
+      </c>
       <c r="H8" s="4" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>28.27</v>
+        <v>44.22</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP003</t>
+          <t>25中海油租MTN002(绿色)</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>217D</t>
+          <t>1.05Y</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.4741</t>
+          <t>1.5561</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中海油国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B+ 58.17</t>
+          <t>B- 45.00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1936,16 +1928,20 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U8" s="3"/>
-      <c r="V8" s="3"/>
+      <c r="U8" s="4" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="V8" s="4" t="n">
+        <v>1.58</v>
+      </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
@@ -1956,24 +1952,28 @@
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB8" s="3"/>
+          <t>天津市</t>
+        </is>
+      </c>
+      <c r="AB8" s="3" t="inlineStr">
+        <is>
+          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
+        </is>
+      </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD8" s="3"/>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
@@ -1983,7 +1983,7 @@
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
+          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
@@ -1993,7 +1993,7 @@
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK8" s="3"/>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="AM8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN8" s="3" t="inlineStr">
@@ -2019,7 +2019,7 @@
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
@@ -2029,17 +2029,17 @@
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2072,72 +2072,74 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26浔旅02</t>
+          <t>26淮南矿MTN001</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:30</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>283906.SH</t>
+          <t>102683537.IB</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>78.86</v>
+        <v>44.22</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>24浔旅03</t>
+          <t>25淮南矿MTN006</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>3.02Y</t>
+          <t>1.28Y+N</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.9196</t>
+          <t>1.6292</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>1.6400/1.6000</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>湖州南浔文旅发展集团有限公司</t>
+          <t>淮南矿业(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C 29.81</t>
+          <t>C+ 34.82</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2147,7 +2149,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2157,42 +2159,48 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U9" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="n">
+        <v>4.92</v>
+      </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X9" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X9" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>安徽省-淮南市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期债券为上述无异议函下第二期发行,发行金额为不超过5.60亿元(含),发行后募集资金将用于偿还到期的公司债券本金。[23浔旅02]</t>
+          <t>本期债务融资工具募集资金10亿元，其中5亿元拟用于集团本部及子公司偿还有息债务，5亿元拟用于集团本部及子公司补充营运资金。</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,德邦证券股份有限公司</t>
+          <t>招商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2202,75 +2210,75 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>湖州南浔文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>淮南矿业(集团)有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO9" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP9" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ9" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR9" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS9" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT9" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU9" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO9" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP9" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ9" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR9" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS9" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT9" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU9" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV9" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2278,7 +2286,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2296,57 +2304,59 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26淳安02</t>
+          <t>26国新保理SCP007</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>283908.SH</t>
+          <t>012682208.IB</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="F10" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.32 ~ 1.52</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>2.07</v>
+        <v>1.52</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>66.86</v>
+        <v>32.84</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>26淳安01</t>
+          <t>25国保01</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>293D</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.9466</t>
+          <t>1.5446</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
@@ -2356,12 +2366,12 @@
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司</t>
+          <t>国新商业保理有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>D+ 6.50</t>
+          <t>C- 22.89</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2371,7 +2381,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2384,109 +2394,119 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U10" s="3"/>
+      <c r="U10" s="4" t="n">
+        <v>0.44</v>
+      </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
           <t>6+</t>
         </is>
       </c>
-      <c r="X10" s="3"/>
+      <c r="X10" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.56%</t>
+        </is>
+      </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
+          <t>发行人注册80亿元超短期融资券,本次发行10亿元,拟用于偿还有息负债[25国新保理SCP006]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>国新商业保理有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK10" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-04</t>
+        </is>
+      </c>
+      <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO10" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP10" s="3"/>
+      <c r="AQ10" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR10" s="3" t="inlineStr">
+        <is>
+          <t>保理</t>
+        </is>
+      </c>
+      <c r="AS10" s="3" t="inlineStr">
+        <is>
+          <t>保理</t>
+        </is>
+      </c>
+      <c r="AT10" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU10" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO10" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP10" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ10" s="3"/>
-      <c r="AR10" s="3"/>
-      <c r="AS10" s="3"/>
-      <c r="AT10" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU10" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV10" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -2507,77 +2527,77 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ10" s="3"/>
+      <c r="AZ10" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26清浦02</t>
+          <t>26广发银行债02</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>283882.SH</t>
+          <t>212680036.IB</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t>1.80 ~ 2.80</t>
-        </is>
-      </c>
+        <v>100.0</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="G11" s="3"/>
       <c r="H11" s="4" t="n">
-        <v>2.12</v>
+        <v>1.57</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>71.86</v>
+        <v>32.22</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26清浦01</t>
+          <t>26广发银行债01BC</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>2.1514</t>
+          <t>1.5714</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>2.1800/2.1600</t>
+          <t>1.5750/1.5700</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>淮安市清江浦融合投资控股集团有限公司</t>
+          <t>广发银行股份有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.21</t>
+          <t>S- 87.02</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2587,7 +2607,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:30</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2604,70 +2624,66 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X11" s="3"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X11" s="3" t="inlineStr">
+        <is>
+          <t>1.54%~1.64%</t>
+        </is>
+      </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还存量公司债券到期本金[23清浦03]</t>
-        </is>
-      </c>
-      <c r="AC11" s="3" t="inlineStr">
-        <is>
-          <t>天风证券股份有限公司,财通证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC11" s="3"/>
       <c r="AD11" s="3"/>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>淮安市清江浦融合投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>广发银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK11" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM11" s="3" t="inlineStr">
@@ -2682,32 +2698,32 @@
       </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>7.5*无效</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>基础设施投融资</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>城市基础设施投融资建设</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2740,7 +2756,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26余产K2</t>
+          <t>26古都01</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2750,7 +2766,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>520462.SZ</t>
+          <t>283920.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
@@ -2759,38 +2775,40 @@
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="3"/>
+        <v>3.0</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>3.0</v>
+      </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>1.40 ~ 2.40</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>54.86</v>
+        <v>89.86</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>26余产K1</t>
+          <t>24古都01</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>2.51Y+2.00Y</t>
+          <t>358D</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>1.7654</t>
+          <t>2.3885</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
@@ -2800,12 +2818,12 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭产业投资发展有限公司</t>
+          <t>洛阳古都发展集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>C+ 32.00</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2825,43 +2843,45 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U12" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="n">
+        <v>3.6</v>
+      </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X12" s="3" t="inlineStr">
-        <is>
-          <t>1.85%~1.95%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X12" s="3"/>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>河南省-洛阳市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后全部用于科技创新领域的股权投资和基金出资,包含置换前期出资和新增出资等,置换后的资金将用于符合国家宏观调控和产业政策要求的用途,不直接或者间接用于缴纳土地出让金。发行人拟将本期债券募集资金全部用于置换前期出资的基金或投资项目,其中拟用于置换基金出资33,700万元,拟用于置换股权直投项目出资16,300万元,总金额不超过5.00亿元。[杭州君联良道股权投资合伙企业(有限合伙),浙江千帆企航贰号股权投资基金合伙企业(有限合伙),杭州元璟新创中小创业投资合伙企业(有限合伙),杭州杭实低空产业私募基金合伙企业(有限合伙),钛虎机器人科技(上海)有限公司,杭州佳量脑科学股份有限公司,灵伴科技(杭州)股份有限公司]</t>
+          <t>本次债券募集资金不超过3亿元(含3亿元)。本次债券募集资金扣除发行费用后拟全部用于偿还“23古都01”债券本金。[23 古都01]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>华泰联合证券有限责任公司,财通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3"/>
+          <t>中原证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3" t="inlineStr">
+        <is>
+          <t>河南省中豫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2874,12 +2894,12 @@
       </c>
       <c r="AG12" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭产业投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>洛阳古都发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
@@ -2889,10 +2909,14 @@
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK12" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK12" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL12" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2900,22 +2924,22 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO12" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ12" s="3" t="inlineStr">
@@ -2935,7 +2959,7 @@
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr">
@@ -2945,7 +2969,7 @@
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
@@ -2968,7 +2992,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y7</t>
+          <t>26古厝12</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -2978,62 +3002,62 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>283876.SH</t>
+          <t>246004.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>9.0</v>
+        <v>6.8</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.99</v>
+        <v>1.82</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>74.22</v>
+        <v>13.96</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y6</t>
+          <t>26古厝11</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>4.94Y+5.00Y</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>2.0599</t>
+          <t>1.8095</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.8100</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>B- 38.49</t>
+          <t>C+ 33.64</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3053,21 +3077,19 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U13" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="n">
+        <v>4.15</v>
+      </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X13" s="3" t="inlineStr">
-        <is>
-          <t>1.92%~2.02%</t>
-        </is>
-      </c>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X13" s="3"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -3076,17 +3098,17 @@
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+          <t>本期债券发行金额为不超过人民币6.80亿元(含6.80亿元)。本期债券的募集资金扣除相关发行费用后,拟全部用于偿还到期债务。[25古厝01,23古厝04,25古厝D6,24福州古厝MTN005,25福州古厝MTN003,23福州古厝MTN001]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
+          <t>中国国际金融股份有限公司,天风证券股份有限公司,华福证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3107,17 +3129,17 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2036-09-08</t>
         </is>
       </c>
       <c r="AK13" s="3"/>
@@ -3133,42 +3155,30 @@
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ13" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR13" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS13" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3"/>
+      <c r="AR13" s="3"/>
+      <c r="AS13" s="3"/>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>钢铁</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3178,12 +3188,12 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY13" s="3" t="inlineStr">
@@ -3196,7 +3206,7 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26古都01</t>
+          <t>26淳安02</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -3206,7 +3216,7 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>283920.SH</t>
+          <t>283908.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
@@ -3215,38 +3225,40 @@
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="F14" s="3"/>
+        <v>6.5</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.3</v>
+        <v>2.07</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>89.86</v>
+        <v>66.86</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>24古都01</t>
+          <t>26淳安01</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>358D</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>2.3885</t>
+          <t>1.9466</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
@@ -3256,12 +3268,12 @@
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>洛阳古都发展集团有限公司</t>
+          <t>淳安县国有资产投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>A 80.00</t>
+          <t>D+ 8.10</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3284,40 +3296,38 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U14" s="3"/>
+      <c r="U14" s="4" t="n">
+        <v>2.6769</v>
+      </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X14" s="3"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>河南省-洛阳市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金不超过3亿元(含3亿元)。本次债券募集资金扣除发行费用后拟全部用于偿还“23古都01”债券本金。[23 古都01]</t>
+          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中原证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD14" s="3" t="inlineStr">
-        <is>
-          <t>河南省中豫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -3335,7 +3345,7 @@
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>洛阳古都发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
@@ -3360,7 +3370,7 @@
       </c>
       <c r="AM14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN14" s="3" t="inlineStr">
@@ -3375,29 +3385,17 @@
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3"/>
+      <c r="AT14" s="3" t="inlineStr">
         <is>
           <t>综合</t>
         </is>
       </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AT14" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
       <c r="AU14" s="3" t="inlineStr">
         <is>
           <t/>
@@ -3405,7 +3403,7 @@
       </c>
       <c r="AV14" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW14" s="3" t="inlineStr">
@@ -3428,70 +3426,74 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债02</t>
+          <t>26中兵物资SCP002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>212680036.IB</t>
+          <t>012682209.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>100.0</v>
+        <v>4.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="G15" s="3"/>
+        <v>4.0</v>
+      </c>
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>1.35 ~ 1.55</t>
+        </is>
+      </c>
       <c r="H15" s="4" t="n">
-        <v>1.57</v>
+        <v>1.41</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>32.22</v>
+        <v>21.84</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债01BC</t>
+          <t>26中兵物资SCP001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>266D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5714</t>
+          <t>1.5500</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>1.5750/1.5700</t>
+          <t>--/1.4296</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>S 91.50</t>
+          <t>C 27.50</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3501,7 +3503,7 @@
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:30</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
@@ -3514,16 +3516,18 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U15" s="3"/>
+      <c r="U15" s="4" t="n">
+        <v>2.575</v>
+      </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.64%</t>
+          <t>1.40%~1.44%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
@@ -3534,19 +3538,23 @@
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC15" s="3"/>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金。</t>
+        </is>
+      </c>
+      <c r="AC15" s="3" t="inlineStr">
+        <is>
+          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
       <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
@@ -3561,7 +3569,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司2026年金融债券(第二期)</t>
+          <t>中国兵工物资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3571,13 +3579,13 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2027-06-04</t>
         </is>
       </c>
       <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM15" s="3" t="inlineStr">
@@ -3592,32 +3600,32 @@
       </c>
       <c r="AO15" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP15" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3650,7 +3658,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26国新保理SCP007</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3660,12 +3668,12 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>012682208.IB</t>
+          <t>102683536.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -3676,48 +3684,48 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.52</t>
+          <t>1.50 ~ 1.98</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.52</v>
+        <v>1.98</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>32.84</v>
+        <v>57.86</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>25国保01</t>
+          <t>26晋能煤业MTN014</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>293D</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.5446</t>
+          <t>2.0055</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/1.9900</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>C 25.66</t>
+          <t>B- 39.05</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3744,12 +3752,12 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.52%~1.56%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
@@ -3760,28 +3768,28 @@
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人注册80亿元超短期融资券,本次发行10亿元,拟用于偿还有息负债[25国新保理SCP006]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3791,7 +3799,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司2026年度第七期超短期融资券</t>
+          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3801,10 +3809,14 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -3822,28 +3834,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3871,14 +3887,12 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>26腾景科技MTN001(科创债)</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -3888,60 +3902,64 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683536.IB</t>
+          <t>102683530.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1.08Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.98</t>
-        </is>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>76.34</v>
+      </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN014</t>
+          <t>23咸金03</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>242D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.0055</t>
+          <t>1.9285</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>2.0000/1.9900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>腾景科技股份有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 39.54</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3964,40 +3982,46 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB17" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
         </is>
       </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3"/>
+          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3" t="inlineStr">
+        <is>
+          <t>福建省融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE17" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -4005,7 +4029,7 @@
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4015,7 +4039,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
+          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4025,7 +4049,7 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2027-10-07</t>
         </is>
       </c>
       <c r="AK17" s="3" t="inlineStr">
@@ -4040,7 +4064,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4053,29 +4077,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP17" s="3"/>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>光学光电子</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4085,7 +4105,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
@@ -4103,109 +4123,111 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ17" s="3"/>
+      <c r="AZ17" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26古厝12</t>
+          <t>26国泰海通CP007</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>246004.SH</t>
+          <t>072610176.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.30</t>
-        </is>
-      </c>
+        <v>40.0</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="G18" s="3"/>
       <c r="H18" s="4" t="n">
-        <v>1.82</v>
+        <v>1.5</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>13.96</v>
+        <v>28.27</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>26国泰海通CP003</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t>217D</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>1.4741</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t>1.5000/1.4600</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>B+ 59.79</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="R18" s="3" t="inlineStr">
+        <is>
+          <t>09-04 09:00</t>
+        </is>
+      </c>
+      <c r="S18" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t>26古厝11</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t>4.94Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>1.8095</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t>1.8300/1.8100</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t>福州古厝集团有限公司</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.08</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="R18" s="3" t="inlineStr">
-        <is>
-          <t>09-04 15:00</t>
-        </is>
-      </c>
-      <c r="S18" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U18" s="4" t="n">
-        <v>4.15</v>
-      </c>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U18" s="3"/>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X18" s="3"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
+          <t>1.47%~1.51%</t>
+        </is>
+      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
           <t>AAA</t>
@@ -4214,23 +4236,19 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
-        </is>
-      </c>
-      <c r="AB18" s="3" t="inlineStr">
-        <is>
-          <t>本期债券发行金额为不超过人民币6.80亿元(含6.80亿元)。本期债券的募集资金扣除相关发行费用后,拟全部用于偿还到期债务。[25古厝01,23古厝04,25古厝D6,24福州古厝MTN005,25福州古厝MTN003,23福州古厝MTN001]</t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB18" s="3"/>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,天风证券股份有限公司,华福证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4240,12 +4258,12 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
@@ -4255,48 +4273,60 @@
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2036-09-08</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3"/>
-      <c r="AR18" s="3"/>
-      <c r="AS18" s="3"/>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4304,7 +4334,7 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
@@ -4322,59 +4352,59 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26中海油租MTN001</t>
+          <t>26山钢Y7</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683538.IB</t>
+          <t>283876.SH</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.54 ~ 1.74</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.69</v>
+        <v>1.99</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>44.22</v>
+        <v>74.22</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>25中海油租MTN002(绿色)</t>
+          <t>26山钢Y6</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>1.05Y</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5561</t>
+          <t>2.0599</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4384,12 +4414,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司</t>
+          <t>山东钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B 54.00</t>
+          <t>B- 36.21</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4399,7 +4429,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4413,11 +4443,9 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V19" s="4" t="n">
-        <v>1.58</v>
-      </c>
+        <v>3.58</v>
+      </c>
+      <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
           <t>6+</t>
@@ -4425,7 +4453,7 @@
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.67%~1.77%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4436,43 +4464,43 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
+          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
@@ -4483,7 +4511,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4498,32 +4526,32 @@
       </c>
       <c r="AO19" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4538,12 +4566,12 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY19" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-04.xlsx
+++ b/data/credit_bond_all_2026-09-04.xlsx
@@ -953,8 +953,12 @@
           <t>1.30 ~ 1.80</t>
         </is>
       </c>
-      <c r="H4" s="3"/>
-      <c r="I4" s="3"/>
+      <c r="H4" s="4" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>31.83</v>
+      </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
           <t>1.55</t>
@@ -1010,7 +1014,9 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="U4" s="3"/>
+      <c r="U4" s="4" t="n">
+        <v>4.18</v>
+      </c>
       <c r="V4" s="3"/>
       <c r="W4" s="3" t="inlineStr">
         <is>
@@ -3658,7 +3664,7 @@
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>26腾景科技MTN001(科创债)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -3668,64 +3674,64 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683536.IB</t>
+          <t>102683530.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>1.08Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.98</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>1.98</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>57.86</v>
+        <v>76.34</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN014</t>
+          <t>23咸金03</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>242D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>2.0055</t>
+          <t>1.9285</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>2.0000/1.9900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>腾景科技股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>B- 39.05</t>
+          <t>E 0.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3748,40 +3754,46 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB16" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
         </is>
       </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>福建省融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
           <t>中期票据</t>
@@ -3789,7 +3801,7 @@
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3799,7 +3811,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
+          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3809,7 +3821,7 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2027-10-07</t>
         </is>
       </c>
       <c r="AK16" s="3" t="inlineStr">
@@ -3824,7 +3836,7 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
@@ -3837,29 +3849,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>光学光电子</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3869,7 +3877,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3887,79 +3895,77 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26腾景科技MTN001(科创债)</t>
+          <t>26国泰海通CP007</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>102683530.IB</t>
+          <t>072610176.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>1.08Y</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
+        <v>40.0</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="4" t="n">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>76.34</v>
+        <v>28.27</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>23咸金03</t>
+          <t>26国泰海通CP003</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>242D</t>
+          <t>217D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.9285</t>
+          <t>1.4741</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4600</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>B+ 59.79</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3982,54 +3988,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U17" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
-        </is>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB17" s="3"/>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD17" s="3" t="inlineStr">
-        <is>
-          <t>福建省融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG17" s="3" t="inlineStr">
@@ -4039,7 +4035,7 @@
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
+          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
@@ -4049,14 +4045,10 @@
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-10-07</t>
-        </is>
-      </c>
-      <c r="AK17" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-04-28</t>
+        </is>
+      </c>
+      <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -4064,7 +4056,7 @@
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN17" s="3" t="inlineStr">
@@ -4074,28 +4066,32 @@
       </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP17" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>光学光电子</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4105,7 +4101,7 @@
       </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW17" s="3" t="inlineStr">
@@ -4123,77 +4119,79 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ17" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ17" s="3"/>
     </row>
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP007</t>
+          <t>26山钢Y7</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>072610176.IB</t>
+          <t>283876.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>40.0</v>
+        <v>9.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G18" s="3"/>
+        <v>9.0</v>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.30</t>
+        </is>
+      </c>
       <c r="H18" s="4" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>28.27</v>
+        <v>74.22</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP003</t>
+          <t>26山钢Y6</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>217D</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>1.4741</t>
+          <t>2.0599</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>山东钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.79</t>
+          <t>B- 36.21</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4203,7 +4201,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4216,16 +4214,18 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U18" s="3"/>
+      <c r="U18" s="4" t="n">
+        <v>3.58</v>
+      </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
@@ -4236,19 +4236,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB18" s="3"/>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB18" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+        </is>
+      </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4258,68 +4262,68 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
+          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO18" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4334,12 +4338,12 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY18" s="3" t="inlineStr">
@@ -4352,59 +4356,59 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y7</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>283876.SH</t>
+          <t>102683536.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.50 ~ 1.98</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>74.22</v>
+        <v>57.86</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y6</t>
+          <t>26晋能煤业MTN014</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.0599</t>
+          <t>2.0055</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4414,12 +4418,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 36.21</t>
+          <t>B- 39.05</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4429,7 +4433,7 @@
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
@@ -4443,12 +4447,12 @@
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>3.58</v>
+        <v>0.43</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
@@ -4464,23 +4468,23 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
@@ -4490,75 +4494,79 @@
       </c>
       <c r="AG19" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
+          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK19" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK19" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV19" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4566,12 +4574,12 @@
       </c>
       <c r="AW19" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX19" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY19" s="3" t="inlineStr">

--- a/data/credit_bond_all_2026-09-04.xlsx
+++ b/data/credit_bond_all_2026-09-04.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-08" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-09" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-08</t>
+          <t>数据来源：DM    2026-09-09</t>
         </is>
       </c>
     </row>
@@ -692,7 +692,7 @@
     <row r="3" customHeight="true" ht="18.0">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>26智光01</t>
+          <t>26清浦02</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -702,7 +702,7 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>283851.SH</t>
+          <t>283882.SH</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
@@ -711,53 +711,55 @@
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F3" s="3"/>
+        <v>1.5</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>1.5</v>
+      </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>2.00 ~ 3.00</t>
+          <t>1.80 ~ 2.80</t>
         </is>
       </c>
       <c r="H3" s="4" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>75.86</v>
+        <v>71.86</v>
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>25智光02</t>
+          <t>26清浦01</t>
         </is>
       </c>
       <c r="L3" s="3" t="inlineStr">
         <is>
-          <t>4.06Y+5.00Y</t>
+          <t>4.92Y</t>
         </is>
       </c>
       <c r="M3" s="3" t="inlineStr">
         <is>
-          <t>2.1600</t>
+          <t>2.1514</t>
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.1800/2.1600</t>
         </is>
       </c>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>泰兴市智光环保科技有限公司</t>
+          <t>淮安市清江浦融合投资控股集团有限公司</t>
         </is>
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C- 24.77</t>
+          <t>C+ 33.25</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -777,47 +779,41 @@
       </c>
       <c r="T3" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U3" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U3" s="4" t="n">
+        <v>3.07</v>
+      </c>
       <c r="V3" s="3"/>
       <c r="W3" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
-        </is>
-      </c>
-      <c r="X3" s="3" t="inlineStr">
-        <is>
-          <t>2.46%~2.56%</t>
-        </is>
-      </c>
+          <t>7-</t>
+        </is>
+      </c>
+      <c r="X3" s="3"/>
       <c r="Y3" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z3" s="3"/>
       <c r="AA3" s="3" t="inlineStr">
         <is>
-          <t>江苏省-泰州市</t>
+          <t>江苏省-淮安市</t>
         </is>
       </c>
       <c r="AB3" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后，用于置换发行人已偿还到期公司债券本金的资金。本期债券募集资金2.60 亿元用于置换发行人已偿还到期公司债券本金的资金[23 智光01]</t>
+          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还存量公司债券到期本金[23清浦03]</t>
         </is>
       </c>
       <c r="AC3" s="3" t="inlineStr">
         <is>
-          <t>中国银河证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD3" s="3" t="inlineStr">
-        <is>
-          <t>四川省金玉融资担保有限公司</t>
-        </is>
-      </c>
+          <t>天风证券股份有限公司,财通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD3" s="3"/>
       <c r="AE3" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -835,7 +831,7 @@
       </c>
       <c r="AH3" s="3" t="inlineStr">
         <is>
-          <t>泰兴市智光环保科技有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
+          <t>淮安市清江浦融合投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI3" s="3" t="inlineStr">
@@ -845,63 +841,67 @@
       </c>
       <c r="AJ3" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
-        </is>
-      </c>
-      <c r="AK3" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK3" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL3" s="3" t="inlineStr">
         <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="AM3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN3" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO3" s="3" t="inlineStr">
+        <is>
+          <t>城投</t>
+        </is>
+      </c>
+      <c r="AP3" s="3" t="inlineStr">
+        <is>
+          <t>7.5*无效</t>
+        </is>
+      </c>
+      <c r="AQ3" s="3" t="inlineStr">
+        <is>
+          <t>基础设施投融资</t>
+        </is>
+      </c>
+      <c r="AR3" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AS3" s="3" t="inlineStr">
+        <is>
+          <t>城市基础设施投融资建设</t>
+        </is>
+      </c>
+      <c r="AT3" s="3" t="inlineStr">
+        <is>
+          <t>基础建设</t>
+        </is>
+      </c>
+      <c r="AU3" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM3" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AN3" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO3" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP3" s="3" t="inlineStr">
-        <is>
-          <t>7.5</t>
-        </is>
-      </c>
-      <c r="AQ3" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR3" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AS3" s="3" t="inlineStr">
-        <is>
-          <t>园区开发运营</t>
-        </is>
-      </c>
-      <c r="AT3" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU3" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV3" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW3" s="3" t="inlineStr">
@@ -924,59 +924,59 @@
     <row r="4" customHeight="true" ht="18.0">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP004</t>
+          <t>26中海油租MTN001</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>012682210.IB</t>
+          <t>102683538.IB</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.54 ~ 1.74</t>
         </is>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1.51</v>
+        <v>1.69</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>31.83</v>
+        <v>44.22</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP003</t>
+          <t>25中海油租MTN002(绿色)</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t>235D</t>
+          <t>1.05Y</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t>1.5483</t>
+          <t>1.5561</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
@@ -986,12 +986,12 @@
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司</t>
+          <t>中海油国际融资租赁有限公司</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t>D+ 7.67</t>
+          <t>B- 45.17</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
@@ -1011,21 +1011,23 @@
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U4" s="4" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="V4" s="3"/>
+        <v>1.58</v>
+      </c>
+      <c r="V4" s="4" t="n">
+        <v>1.58</v>
+      </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.67%~1.77%</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
@@ -1036,23 +1038,23 @@
       <c r="Z4" s="3"/>
       <c r="AA4" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB4" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务[26东北电力SCP001]</t>
+          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
         </is>
       </c>
       <c r="AC4" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD4" s="3"/>
       <c r="AE4" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF4" s="3" t="inlineStr">
@@ -1067,7 +1069,7 @@
       </c>
       <c r="AH4" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司2026年度第四期超短期融资券</t>
+          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI4" s="3" t="inlineStr">
@@ -1077,17 +1079,13 @@
       </c>
       <c r="AJ4" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
-        </is>
-      </c>
-      <c r="AK4" s="3" t="inlineStr">
-        <is>
-          <t>休2</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK4" s="3"/>
       <c r="AL4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM4" s="3" t="inlineStr">
@@ -1097,37 +1095,37 @@
       </c>
       <c r="AN4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO4" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP4" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AQ4" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR4" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>融资租赁</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>多元金融</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr">
@@ -1152,7 +1150,7 @@
       </c>
       <c r="AY4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AZ4" s="3"/>
@@ -1160,72 +1158,74 @@
     <row r="5" customHeight="true" ht="18.0">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>26浔旅02</t>
+          <t>26淮南矿MTN001</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:30</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>283906.SH</t>
+          <t>102683537.IB</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="F5" s="3"/>
+        <v>10.0</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>10.0</v>
+      </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.70</t>
+          <t>1.30 ~ 2.10</t>
         </is>
       </c>
       <c r="H5" s="4" t="n">
-        <v>2.19</v>
+        <v>1.69</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>78.86</v>
+        <v>44.22</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>24浔旅03</t>
+          <t>25淮南矿MTN006</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>3.02Y</t>
+          <t>1.28Y+N</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>1.9196</t>
+          <t>1.6292</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>--/1.8000</t>
+          <t>1.6400/1.6000</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>湖州南浔文旅发展集团有限公司</t>
+          <t>淮南矿业(集团)有限责任公司</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>C 29.80</t>
+          <t>B- 38.75</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
@@ -1245,42 +1245,48 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="U5" s="3"/>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="n">
+        <v>4.92</v>
+      </c>
       <c r="V5" s="3"/>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="X5" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X5" s="3" t="inlineStr">
+        <is>
+          <t>1.76%~1.86%</t>
+        </is>
+      </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z5" s="3"/>
       <c r="AA5" s="3" t="inlineStr">
         <is>
-          <t>浙江省-湖州市</t>
+          <t>安徽省-淮南市</t>
         </is>
       </c>
       <c r="AB5" s="3" t="inlineStr">
         <is>
-          <t>本期债券为上述无异议函下第二期发行,发行金额为不超过5.60亿元(含),发行后募集资金将用于偿还到期的公司债券本金。[23浔旅02]</t>
+          <t>本期债务融资工具募集资金10亿元，其中5亿元拟用于集团本部及子公司偿还有息债务，5亿元拟用于集团本部及子公司补充营运资金。</t>
         </is>
       </c>
       <c r="AC5" s="3" t="inlineStr">
         <is>
-          <t>财通证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,德邦证券股份有限公司</t>
+          <t>招商银行股份有限公司,杭州银行股份有限公司</t>
         </is>
       </c>
       <c r="AD5" s="3"/>
       <c r="AE5" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF5" s="3" t="inlineStr">
@@ -1290,75 +1296,75 @@
       </c>
       <c r="AG5" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH5" s="3" t="inlineStr">
         <is>
-          <t>湖州南浔文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>淮南矿业(集团)有限责任公司2026年度第一期中期票据</t>
         </is>
       </c>
       <c r="AI5" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ5" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK5" s="3"/>
       <c r="AL5" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN5" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO5" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP5" s="3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AQ5" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR5" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS5" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT5" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU5" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN5" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="AO5" s="3" t="inlineStr">
-        <is>
-          <t>类城投</t>
-        </is>
-      </c>
-      <c r="AP5" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AQ5" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR5" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS5" s="3" t="inlineStr">
-        <is>
-          <t>其他基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT5" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU5" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV5" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1366,7 +1372,7 @@
       </c>
       <c r="AW5" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX5" s="3" t="inlineStr">
@@ -1384,74 +1390,74 @@
     <row r="6" customHeight="true" ht="18.0">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>26清浦02</t>
+          <t>26国新保理SCP007</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>283882.SH</t>
+          <t>012682208.IB</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>1.5</v>
+        <v>10.0</v>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>1.80 ~ 2.80</t>
+          <t>1.32 ~ 1.52</t>
         </is>
       </c>
       <c r="H6" s="4" t="n">
-        <v>2.12</v>
+        <v>1.52</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>71.86</v>
+        <v>32.84</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>26清浦01</t>
+          <t>25国保01</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t>4.92Y</t>
+          <t>293D</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t>2.1514</t>
+          <t>1.5446</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t>2.1800/2.1600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>淮安市清江浦融合投资控股集团有限公司</t>
+          <t>国新商业保理有限公司</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C 27.83</t>
+          <t>C 29.95</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1461,7 +1467,7 @@
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
@@ -1475,122 +1481,118 @@
         </is>
       </c>
       <c r="U6" s="4" t="n">
-        <v>3.07</v>
+        <v>0.44</v>
       </c>
       <c r="V6" s="3"/>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t>7-</t>
-        </is>
-      </c>
-      <c r="X6" s="3"/>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X6" s="3" t="inlineStr">
+        <is>
+          <t>1.52%~1.56%</t>
+        </is>
+      </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z6" s="3"/>
       <c r="AA6" s="3" t="inlineStr">
         <is>
-          <t>江苏省-淮安市</t>
+          <t>天津市</t>
         </is>
       </c>
       <c r="AB6" s="3" t="inlineStr">
         <is>
-          <t>本期公司债券募集资金扣除发行费用后,拟用于偿还存量公司债券到期本金[23清浦03]</t>
+          <t>发行人注册80亿元超短期融资券,本次发行10亿元,拟用于偿还有息负债[25国新保理SCP006]</t>
         </is>
       </c>
       <c r="AC6" s="3" t="inlineStr">
         <is>
-          <t>天风证券股份有限公司,财通证券股份有限公司</t>
+          <t>渤海银行股份有限公司</t>
         </is>
       </c>
       <c r="AD6" s="3"/>
       <c r="AE6" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF6" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG6" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH6" s="3" t="inlineStr">
         <is>
-          <t>淮安市清江浦融合投资控股集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>国新商业保理有限公司2026年度第七期超短期融资券</t>
         </is>
       </c>
       <c r="AI6" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ6" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK6" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-04</t>
+        </is>
+      </c>
+      <c r="AK6" s="3"/>
       <c r="AL6" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN6" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO6" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP6" s="3"/>
+      <c r="AQ6" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR6" s="3" t="inlineStr">
+        <is>
+          <t>保理</t>
+        </is>
+      </c>
+      <c r="AS6" s="3" t="inlineStr">
+        <is>
+          <t>保理</t>
+        </is>
+      </c>
+      <c r="AT6" s="3" t="inlineStr">
+        <is>
+          <t>多元金融</t>
+        </is>
+      </c>
+      <c r="AU6" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN6" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO6" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP6" s="3" t="inlineStr">
-        <is>
-          <t>7.5*无效</t>
-        </is>
-      </c>
-      <c r="AQ6" s="3" t="inlineStr">
-        <is>
-          <t>基础设施投融资</t>
-        </is>
-      </c>
-      <c r="AR6" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AS6" s="3" t="inlineStr">
-        <is>
-          <t>城市基础设施投融资建设</t>
-        </is>
-      </c>
-      <c r="AT6" s="3" t="inlineStr">
-        <is>
-          <t>基础建设</t>
-        </is>
-      </c>
-      <c r="AU6" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV6" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -1611,77 +1613,77 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ6" s="3"/>
+      <c r="AZ6" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="7" customHeight="true" ht="18.0">
       <c r="A7" s="3" t="inlineStr">
         <is>
-          <t>26余产K2</t>
+          <t>26广发银行债02</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>520462.SZ</t>
+          <t>212680036.IB</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3Y</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3" t="inlineStr">
-        <is>
-          <t>1.40 ~ 2.40</t>
-        </is>
-      </c>
+        <v>100.0</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="G7" s="3"/>
       <c r="H7" s="4" t="n">
-        <v>1.95</v>
+        <v>1.57</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>54.86</v>
+        <v>32.22</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t>26余产K1</t>
+          <t>26广发银行债01BC</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t>2.51Y+2.00Y</t>
+          <t>2.90Y</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>1.7654</t>
+          <t>1.5714</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5750/1.5700</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭产业投资发展有限公司</t>
+          <t>广发银行股份有限公司</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>D 5.00</t>
+          <t>S 90.39</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -1691,7 +1693,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:30</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
@@ -1701,19 +1703,19 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U7" s="3"/>
       <c r="V7" s="3"/>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>3</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t>1.85%~1.95%</t>
+          <t>1.54%~1.64%</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
@@ -1724,54 +1726,50 @@
       <c r="Z7" s="3"/>
       <c r="AA7" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>广东省-广州市</t>
         </is>
       </c>
       <c r="AB7" s="3" t="inlineStr">
         <is>
-          <t>本期债券募集资金扣除发行费用后全部用于科技创新领域的股权投资和基金出资,包含置换前期出资和新增出资等,置换后的资金将用于符合国家宏观调控和产业政策要求的用途,不直接或者间接用于缴纳土地出让金。发行人拟将本期债券募集资金全部用于置换前期出资的基金或投资项目,其中拟用于置换基金出资33,700万元,拟用于置换股权直投项目出资16,300万元,总金额不超过5.00亿元。[杭州君联良道股权投资合伙企业(有限合伙),浙江千帆企航贰号股权投资基金合伙企业(有限合伙),杭州元璟新创中小创业投资合伙企业(有限合伙),杭州杭实低空产业私募基金合伙企业(有限合伙),钛虎机器人科技(上海)有限公司,杭州佳量脑科学股份有限公司,灵伴科技(杭州)股份有限公司]</t>
-        </is>
-      </c>
-      <c r="AC7" s="3" t="inlineStr">
-        <is>
-          <t>华泰联合证券有限责任公司,财通证券股份有限公司</t>
-        </is>
-      </c>
+          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
+        </is>
+      </c>
+      <c r="AC7" s="3"/>
       <c r="AD7" s="3"/>
       <c r="AE7" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>商业银行普通债券</t>
         </is>
       </c>
       <c r="AF7" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG7" s="3" t="inlineStr">
         <is>
-          <t>深交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH7" s="3" t="inlineStr">
         <is>
-          <t>杭州余杭产业投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
+          <t>广发银行股份有限公司2026年金融债券(第二期)</t>
         </is>
       </c>
       <c r="AI7" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ7" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK7" s="3"/>
       <c r="AL7" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM7" s="3" t="inlineStr">
@@ -1781,37 +1779,37 @@
       </c>
       <c r="AN7" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO7" s="3" t="inlineStr">
         <is>
-          <t>类城投</t>
+          <t>金融</t>
         </is>
       </c>
       <c r="AP7" s="3" t="inlineStr">
         <is>
-          <t>6.5*无效</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AQ7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AR7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>商业银行</t>
         </is>
       </c>
       <c r="AS7" s="3" t="inlineStr">
         <is>
-          <t>国资经营</t>
+          <t>股份制银行</t>
         </is>
       </c>
       <c r="AT7" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="AU7" s="3" t="inlineStr">
@@ -1844,59 +1842,59 @@
     <row r="8" customHeight="true" ht="18.0">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>26中海油租MTN001</t>
+          <t>26古都01</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t>102683538.IB</t>
+          <t>283920.SH</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>10.0</v>
+        <v>3.0</v>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>1.54 ~ 1.74</t>
+          <t>2.30 ~ 3.30</t>
         </is>
       </c>
       <c r="H8" s="4" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>44.22</v>
+        <v>89.86</v>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>25中海油租MTN002(绿色)</t>
+          <t>24古都01</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t>1.05Y</t>
+          <t>358D</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>1.5561</t>
+          <t>2.3885</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
@@ -1906,12 +1904,12 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司</t>
+          <t>洛阳古都发展集团有限公司</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t>B- 45.00</t>
+          <t>C+ 32.00</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
@@ -1921,7 +1919,7 @@
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
@@ -1935,82 +1933,84 @@
         </is>
       </c>
       <c r="U8" s="4" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="V8" s="4" t="n">
-        <v>1.58</v>
-      </c>
+        <v>3.6</v>
+      </c>
+      <c r="V8" s="3"/>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t>1.67%~1.77%</t>
-        </is>
-      </c>
+          <t>8+</t>
+        </is>
+      </c>
+      <c r="X8" s="3"/>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z8" s="3"/>
       <c r="AA8" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>河南省-洛阳市</t>
         </is>
       </c>
       <c r="AB8" s="3" t="inlineStr">
         <is>
-          <t>本期中期票据发行规模10亿元,全部用于偿还存量银行贷款,穿透用于集团内部炼化租赁项目</t>
+          <t>本次债券募集资金不超过3亿元(含3亿元)。本次债券募集资金扣除发行费用后拟全部用于偿还“23古都01”债券本金。[23 古都01]</t>
         </is>
       </c>
       <c r="AC8" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,中国工商银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD8" s="3"/>
+          <t>中原证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD8" s="3" t="inlineStr">
+        <is>
+          <t>河南省中豫融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE8" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF8" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG8" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH8" s="3" t="inlineStr">
         <is>
-          <t>中海油国际融资租赁有限公司2026年度第一期中期票据</t>
+          <t>洛阳古都发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
         </is>
       </c>
       <c r="AI8" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ8" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK8" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK8" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AN8" s="3" t="inlineStr">
@@ -2020,32 +2020,32 @@
       </c>
       <c r="AO8" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP8" s="3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="AQ8" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR8" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS8" s="3" t="inlineStr">
         <is>
-          <t>融资租赁</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT8" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU8" s="3" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="AV8" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW8" s="3" t="inlineStr">
@@ -2078,74 +2078,74 @@
     <row r="9" customHeight="true" ht="18.0">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>26淮南矿MTN001</t>
+          <t>26余产K2</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>102683537.IB</t>
+          <t>520462.SZ</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 2.10</t>
+          <t>1.40 ~ 2.40</t>
         </is>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1.69</v>
+        <v>1.95</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>44.22</v>
+        <v>54.86</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.96</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>25淮南矿MTN006</t>
+          <t>26余产K1</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>1.28Y+N</t>
+          <t>2.51Y+2.00Y</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>1.6292</t>
+          <t>1.7654</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>1.6400/1.6000</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>淮南矿业(集团)有限责任公司</t>
+          <t>杭州余杭产业投资发展有限公司</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t>C+ 34.82</t>
+          <t>D- 2.50</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
@@ -2155,7 +2155,7 @@
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
@@ -2165,21 +2165,21 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U9" s="4" t="n">
-        <v>4.92</v>
+        <v>2.32</v>
       </c>
       <c r="V9" s="3"/>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>6</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t>1.76%~1.86%</t>
+          <t>1.85%~1.95%</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
@@ -2190,23 +2190,23 @@
       <c r="Z9" s="3"/>
       <c r="AA9" s="3" t="inlineStr">
         <is>
-          <t>安徽省-淮南市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB9" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具募集资金10亿元，其中5亿元拟用于集团本部及子公司偿还有息债务，5亿元拟用于集团本部及子公司补充营运资金。</t>
+          <t>本期债券募集资金扣除发行费用后全部用于科技创新领域的股权投资和基金出资,包含置换前期出资和新增出资等,置换后的资金将用于符合国家宏观调控和产业政策要求的用途,不直接或者间接用于缴纳土地出让金。发行人拟将本期债券募集资金全部用于置换前期出资的基金或投资项目,其中拟用于置换基金出资33,700万元,拟用于置换股权直投项目出资16,300万元,总金额不超过5.00亿元。[杭州君联良道股权投资合伙企业(有限合伙),浙江千帆企航贰号股权投资基金合伙企业(有限合伙),杭州元璟新创中小创业投资合伙企业(有限合伙),杭州杭实低空产业私募基金合伙企业(有限合伙),钛虎机器人科技(上海)有限公司,杭州佳量脑科学股份有限公司,灵伴科技(杭州)股份有限公司]</t>
         </is>
       </c>
       <c r="AC9" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,杭州银行股份有限公司</t>
+          <t>华泰联合证券有限责任公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD9" s="3"/>
       <c r="AE9" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF9" s="3" t="inlineStr">
@@ -2216,68 +2216,68 @@
       </c>
       <c r="AG9" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>深交所</t>
         </is>
       </c>
       <c r="AH9" s="3" t="inlineStr">
         <is>
-          <t>淮南矿业(集团)有限责任公司2026年度第一期中期票据</t>
+          <t>杭州余杭产业投资发展有限公司2026年面向专业投资者非公开发行科技创新公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI9" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ9" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK9" s="3"/>
       <c r="AL9" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM9" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN9" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN9" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO9" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP9" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6.5*无效</t>
         </is>
       </c>
       <c r="AQ9" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AR9" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>国资经营</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="AW9" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX9" s="3" t="inlineStr">
@@ -2310,74 +2310,74 @@
     <row r="10" customHeight="true" ht="18.0">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>26国新保理SCP007</t>
+          <t>26浔旅02</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 17:30</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>012682208.IB</t>
+          <t>283906.SH</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>10.0</v>
+        <v>5.6</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>10.0</v>
+        <v>5.6</v>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>1.32 ~ 1.52</t>
+          <t>1.70 ~ 2.70</t>
         </is>
       </c>
       <c r="H10" s="4" t="n">
-        <v>1.52</v>
+        <v>2.19</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>32.84</v>
+        <v>78.86</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>25国保01</t>
+          <t>24浔旅03</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>293D</t>
+          <t>3.02Y</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>1.5446</t>
+          <t>1.9196</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.8000</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司</t>
+          <t>湖州南浔文旅发展集团有限公司</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t>C- 22.89</t>
+          <t>C 25.54</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
@@ -2397,115 +2397,115 @@
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U10" s="4" t="n">
-        <v>0.44</v>
+        <v>2.2679</v>
       </c>
       <c r="V10" s="3"/>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X10" s="3" t="inlineStr">
-        <is>
-          <t>1.52%~1.56%</t>
-        </is>
-      </c>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X10" s="3"/>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z10" s="3"/>
       <c r="AA10" s="3" t="inlineStr">
         <is>
-          <t>天津市</t>
+          <t>浙江省-湖州市</t>
         </is>
       </c>
       <c r="AB10" s="3" t="inlineStr">
         <is>
-          <t>发行人注册80亿元超短期融资券,本次发行10亿元,拟用于偿还有息负债[25国新保理SCP006]</t>
+          <t>本期债券为上述无异议函下第二期发行,发行金额为不超过5.60亿元(含),发行后募集资金将用于偿还到期的公司债券本金。[23浔旅02]</t>
         </is>
       </c>
       <c r="AC10" s="3" t="inlineStr">
         <is>
-          <t>渤海银行股份有限公司</t>
+          <t>财通证券股份有限公司,国泰海通证券股份有限公司,光大证券股份有限公司,德邦证券股份有限公司</t>
         </is>
       </c>
       <c r="AD10" s="3"/>
       <c r="AE10" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF10" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG10" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH10" s="3" t="inlineStr">
         <is>
-          <t>国新商业保理有限公司2026年度第七期超短期融资券</t>
+          <t>湖州南浔文旅发展集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI10" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ10" s="3" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM10" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN10" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN10" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO10" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP10" s="3"/>
+          <t>类城投</t>
+        </is>
+      </c>
+      <c r="AP10" s="3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="AQ10" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR10" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>保理</t>
+          <t>其他基础设施投融资建设</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>多元金融</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr">
@@ -2533,77 +2533,79 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ10" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ10" s="3"/>
     </row>
     <row r="11" customHeight="true" ht="18.0">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债02</t>
+          <t>26智光01</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>212680036.IB</t>
+          <t>283851.SH</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t>3Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>100.0</v>
+        <v>2.6</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>100.0</v>
-      </c>
-      <c r="G11" s="3"/>
+        <v>2.6</v>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>2.00 ~ 3.00</t>
+        </is>
+      </c>
       <c r="H11" s="4" t="n">
-        <v>1.57</v>
+        <v>2.16</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>32.22</v>
+        <v>75.86</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>26广发银行债01BC</t>
+          <t>25智光02</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>2.90Y</t>
+          <t>4.06Y+5.00Y</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>1.5714</t>
+          <t>2.1600</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>1.5750/1.5700</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司</t>
+          <t>泰兴市智光环保科技有限公司</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>S- 87.02</t>
+          <t>C- 20.88</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2613,7 +2615,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:30</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
@@ -2623,113 +2625,123 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="U11" s="3"/>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="n">
+        <v>4.77</v>
+      </c>
       <c r="V11" s="3"/>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>1.54%~1.64%</t>
+          <t>2.46%~2.56%</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3" t="inlineStr">
         <is>
-          <t>广东省-广州市</t>
+          <t>江苏省-泰州市</t>
         </is>
       </c>
       <c r="AB11" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行的募集资金将依据适用法律和主管部门的批准，用于满足资产负债配置需要，充实资金来源，优化负债期限结构，促进业务的稳健发展。</t>
-        </is>
-      </c>
-      <c r="AC11" s="3"/>
-      <c r="AD11" s="3"/>
+          <t>本期债券募集资金扣除发行费用后，用于置换发行人已偿还到期公司债券本金的资金。本期债券募集资金2.60 亿元用于置换发行人已偿还到期公司债券本金的资金[23 智光01]</t>
+        </is>
+      </c>
+      <c r="AC11" s="3" t="inlineStr">
+        <is>
+          <t>中国银河证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD11" s="3" t="inlineStr">
+        <is>
+          <t>四川省金玉融资担保有限公司</t>
+        </is>
+      </c>
       <c r="AE11" s="3" t="inlineStr">
         <is>
-          <t>商业银行普通债券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF11" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG11" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH11" s="3" t="inlineStr">
         <is>
-          <t>广发银行股份有限公司2026年金融债券(第二期)</t>
+          <t>泰兴市智光环保科技有限公司2026年面向专业投资者非公开发行公司债券(第一期)</t>
         </is>
       </c>
       <c r="AI11" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ11" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3" t="inlineStr">
         <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AM11" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN11" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN11" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO11" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>类城投</t>
         </is>
       </c>
       <c r="AP11" s="3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="AQ11" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础设施投融资</t>
         </is>
       </c>
       <c r="AR11" s="3" t="inlineStr">
         <is>
-          <t>商业银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>股份制银行</t>
+          <t>园区开发运营</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>基础建设</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr">
@@ -2739,7 +2751,7 @@
       </c>
       <c r="AV11" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW11" s="3" t="inlineStr">
@@ -2762,7 +2774,7 @@
     <row r="12" customHeight="true" ht="18.0">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>26古都01</t>
+          <t>26古厝12</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -2772,64 +2784,64 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t>283920.SH</t>
+          <t>246004.SH</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>5+5</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>3.0</v>
+        <v>6.8</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>3.0</v>
+        <v>6.8</v>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2.30 ~ 3.30</t>
+          <t>1.50 ~ 2.30</t>
         </is>
       </c>
       <c r="H12" s="4" t="n">
-        <v>2.3</v>
+        <v>1.82</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>89.86</v>
+        <v>13.96</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>--</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>24古都01</t>
+          <t>26古厝11</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>358D</t>
+          <t>4.94Y+5.00Y</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>2.3885</t>
+          <t>1.8095</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.8300/1.8100</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>洛阳古都发展集团有限公司</t>
+          <t>福州古厝集团有限公司</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 32.00</t>
+          <t>C+ 30.82</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2849,45 +2861,41 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U12" s="4" t="n">
-        <v>3.6</v>
+        <v>4.15</v>
       </c>
       <c r="V12" s="3"/>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>4</t>
         </is>
       </c>
       <c r="X12" s="3"/>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z12" s="3"/>
       <c r="AA12" s="3" t="inlineStr">
         <is>
-          <t>河南省-洛阳市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB12" s="3" t="inlineStr">
         <is>
-          <t>本次债券募集资金不超过3亿元(含3亿元)。本次债券募集资金扣除发行费用后拟全部用于偿还“23古都01”债券本金。[23 古都01]</t>
+          <t>本期债券发行金额为不超过人民币6.80亿元(含6.80亿元)。本期债券的募集资金扣除相关发行费用后,拟全部用于偿还到期债务。[25古厝01,23古厝04,25古厝D6,24福州古厝MTN005,25福州古厝MTN003,23福州古厝MTN001]</t>
         </is>
       </c>
       <c r="AC12" s="3" t="inlineStr">
         <is>
-          <t>中原证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD12" s="3" t="inlineStr">
-        <is>
-          <t>河南省中豫融资担保有限公司</t>
-        </is>
-      </c>
+          <t>中国国际金融股份有限公司,天风证券股份有限公司,华福证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD12" s="3"/>
       <c r="AE12" s="3" t="inlineStr">
         <is>
           <t>公司债券</t>
@@ -2905,24 +2913,20 @@
       </c>
       <c r="AH12" s="3" t="inlineStr">
         <is>
-          <t>洛阳古都发展集团有限公司2026年面向专业投资者非公开发行公司债券</t>
+          <t>福州古厝集团有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
         </is>
       </c>
       <c r="AI12" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ12" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK12" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2036-09-08</t>
+        </is>
+      </c>
+      <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
           <t/>
@@ -2930,12 +2934,12 @@
       </c>
       <c r="AM12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AO12" s="3" t="inlineStr">
@@ -2945,24 +2949,12 @@
       </c>
       <c r="AP12" s="3" t="inlineStr">
         <is>
-          <t>8.5</t>
-        </is>
-      </c>
-      <c r="AQ12" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AR12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
-      <c r="AS12" s="3" t="inlineStr">
-        <is>
-          <t>国资经营</t>
-        </is>
-      </c>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ12" s="3"/>
+      <c r="AR12" s="3"/>
+      <c r="AS12" s="3"/>
       <c r="AT12" s="3" t="inlineStr">
         <is>
           <t>基础建设</t>
@@ -2970,17 +2962,17 @@
       </c>
       <c r="AU12" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2031-09-08</t>
         </is>
       </c>
       <c r="AV12" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW12" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>含权</t>
         </is>
       </c>
       <c r="AX12" s="3" t="inlineStr">
@@ -2998,7 +2990,7 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26古厝12</t>
+          <t>26淳安02</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -3008,113 +3000,115 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>246004.SH</t>
+          <t>283908.SH</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5+5</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="F13" s="3"/>
+        <v>6.5</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>6.5</v>
+      </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.30</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>1.82</v>
+        <v>2.07</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>13.96</v>
+        <v>66.86</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>2.14</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>26淳安01</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>4.59Y</t>
+        </is>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>1.9466</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
+          <t>--/--</t>
+        </is>
+      </c>
+      <c r="O13" s="3" t="inlineStr">
+        <is>
+          <t>淳安县国有资产投资集团有限公司</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>D+ 8.10</t>
+        </is>
+      </c>
+      <c r="Q13" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="R13" s="3" t="inlineStr">
+        <is>
+          <t>09-04 15:00</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
           <t>--</t>
         </is>
       </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>26古厝11</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
-        <is>
-          <t>4.94Y+5.00Y</t>
-        </is>
-      </c>
-      <c r="M13" s="3" t="inlineStr">
-        <is>
-          <t>1.8095</t>
-        </is>
-      </c>
-      <c r="N13" s="3" t="inlineStr">
-        <is>
-          <t>1.8300/1.8100</t>
-        </is>
-      </c>
-      <c r="O13" s="3" t="inlineStr">
-        <is>
-          <t>福州古厝集团有限公司</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="inlineStr">
-        <is>
-          <t>C+ 33.64</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
-        </is>
-      </c>
-      <c r="R13" s="3" t="inlineStr">
-        <is>
-          <t>09-04 15:00</t>
-        </is>
-      </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t>--</t>
-        </is>
-      </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>4.15</v>
+        <v>2.6769</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X13" s="3"/>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券发行金额为不超过人民币6.80亿元(含6.80亿元)。本期债券的募集资金扣除相关发行费用后,拟全部用于偿还到期债务。[25古厝01,23古厝04,25古厝D6,24福州古厝MTN005,25福州古厝MTN003,23福州古厝MTN001]</t>
+          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>中国国际金融股份有限公司,天风证券股份有限公司,华福证券股份有限公司</t>
+          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
@@ -3135,23 +3129,27 @@
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>福州古厝集团有限公司2026年面向专业投资者公开发行公司债券(第六期)</t>
+          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2036-09-08</t>
-        </is>
-      </c>
-      <c r="AK13" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK13" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3161,7 +3159,7 @@
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO13" s="3" t="inlineStr">
@@ -3171,7 +3169,7 @@
       </c>
       <c r="AP13" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="AQ13" s="3"/>
@@ -3179,12 +3177,12 @@
       <c r="AS13" s="3"/>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>基础建设</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AV13" s="3" t="inlineStr">
@@ -3194,7 +3192,7 @@
       </c>
       <c r="AW13" s="3" t="inlineStr">
         <is>
-          <t>含权</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX13" s="3" t="inlineStr">
@@ -3212,74 +3210,74 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26淳安02</t>
+          <t>26中兵物资SCP002</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>283908.SH</t>
+          <t>012682209.IB</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>6.5</v>
+        <v>4.0</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>6.5</v>
+        <v>4.0</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>2.07</v>
+        <v>1.41</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>66.86</v>
+        <v>21.84</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26淳安01</t>
+          <t>26中兵物资SCP001</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>266D</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.9466</t>
+          <t>1.5500</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4296</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.10</t>
+          <t>B- 40.00</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3289,7 +3287,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3303,75 +3301,75 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.6769</v>
+        <v>2.575</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X14" s="3"/>
+          <t>5-</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t>1.40%~1.44%</t>
+        </is>
+      </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>中国兵工物资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK14" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-04</t>
+        </is>
+      </c>
+      <c r="AK14" s="3"/>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
@@ -3386,20 +3384,32 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>城投</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3"/>
-      <c r="AR14" s="3"/>
-      <c r="AS14" s="3"/>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3" t="inlineStr">
+        <is>
+          <t>贸易零售</t>
+        </is>
+      </c>
+      <c r="AR14" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
+      <c r="AS14" s="3" t="inlineStr">
+        <is>
+          <t>其他贸易</t>
+        </is>
+      </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>综合</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3432,7 +3442,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP002</t>
+          <t>26腾景科技MTN001(科创债)</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3442,64 +3452,64 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>012682209.IB</t>
+          <t>102683530.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>1.08Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 2.00</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>1.41</v>
+        <v>2.0</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>21.84</v>
+        <v>76.34</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP001</t>
+          <t>23咸金03</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>266D</t>
+          <t>242D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.5500</t>
+          <t>1.9285</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/1.4296</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>腾景科技股份有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C 27.50</t>
+          <t>C- 25.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3523,49 +3533,53 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>2.575</v>
+        <v>1.0</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.40%~1.44%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>福建省-福州市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金。</t>
+          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3"/>
+          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3" t="inlineStr">
+        <is>
+          <t>福建省融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3575,7 +3589,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第二期超短期融资券</t>
+          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3585,10 +3599,14 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
-        </is>
-      </c>
-      <c r="AK15" s="3"/>
+          <t>2027-10-07</t>
+        </is>
+      </c>
+      <c r="AK15" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -3596,7 +3614,7 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3609,29 +3627,25 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP15" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
+      <c r="AP15" s="3"/>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>贸易零售</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>其他贸易</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>光学光电子</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3641,7 +3655,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3659,79 +3673,77 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ15" s="3"/>
+      <c r="AZ15" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26腾景科技MTN001(科创债)</t>
+          <t>26国泰海通CP007</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>102683530.IB</t>
+          <t>072610176.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>1.08Y</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>1.0</v>
+        <v>40.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G16" s="3" t="inlineStr">
-        <is>
-          <t>1.50 ~ 2.00</t>
-        </is>
-      </c>
+        <v>40.0</v>
+      </c>
+      <c r="G16" s="3"/>
       <c r="H16" s="4" t="n">
-        <v>2.0</v>
+        <v>1.5</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>76.34</v>
+        <v>28.27</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>23咸金03</t>
+          <t>26国泰海通CP003</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>242D</t>
+          <t>217D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.9285</t>
+          <t>1.4741</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4600</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>E 0.00</t>
+          <t>A- 61.93</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3754,54 +3766,44 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U16" s="4" t="n">
-        <v>1.0</v>
-      </c>
+      <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
-        </is>
-      </c>
-      <c r="AB16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB16" s="3"/>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3" t="inlineStr">
-        <is>
-          <t>福建省融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>国泰海通证券股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3"/>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3811,7 +3813,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
+          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3821,14 +3823,10 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-10-07</t>
-        </is>
-      </c>
-      <c r="AK16" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-04-28</t>
+        </is>
+      </c>
+      <c r="AK16" s="3"/>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -3836,7 +3834,7 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AN16" s="3" t="inlineStr">
@@ -3846,28 +3844,32 @@
       </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP16" s="3"/>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP16" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>非银</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>券商</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>光学光电子</t>
+          <t>证券</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3877,7 +3879,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3895,77 +3897,79 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ16" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ16" s="3"/>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP007</t>
+          <t>26山钢Y7</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>072610176.IB</t>
+          <t>283876.SH</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>40.0</v>
+        <v>9.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G17" s="3"/>
+        <v>9.0</v>
+      </c>
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>1.70 ~ 2.30</t>
+        </is>
+      </c>
       <c r="H17" s="4" t="n">
-        <v>1.5</v>
+        <v>1.99</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>28.27</v>
+        <v>74.22</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP003</t>
+          <t>26山钢Y6</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>217D</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>1.4741</t>
+          <t>2.0599</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>山东钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B+ 59.79</t>
+          <t>B- 36.65</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3975,7 +3979,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3988,16 +3992,18 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U17" s="3"/>
+      <c r="U17" s="4" t="n">
+        <v>3.58</v>
+      </c>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4008,19 +4014,23 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB17" s="3"/>
+          <t>山东省-济南市</t>
+        </is>
+      </c>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+        </is>
+      </c>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4030,68 +4040,68 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
+          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
+          <t>2029-09-07</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t/>
         </is>
       </c>
       <c r="AM17" s="3" t="inlineStr">
         <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO17" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
+          <t>产业</t>
         </is>
       </c>
       <c r="AP17" s="3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ17" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR17" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr">
@@ -4106,12 +4116,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4124,74 +4134,74 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y7</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>283876.SH</t>
+          <t>102683536.IB</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.70 ~ 2.30</t>
+          <t>1.50 ~ 1.98</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>74.22</v>
+        <v>57.86</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y6</t>
+          <t>26晋能煤业MTN014</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.0599</t>
+          <t>2.0055</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/1.9900</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 36.21</t>
+          <t>B- 36.34</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4201,7 +4211,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4215,12 +4225,12 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>3.58</v>
+        <v>0.43</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -4236,23 +4246,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4262,75 +4272,79 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
+          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
-        </is>
-      </c>
-      <c r="AK18" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK18" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL18" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN18" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO18" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP18" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="AQ18" s="3" t="inlineStr">
+        <is>
+          <t>化石能源</t>
+        </is>
+      </c>
+      <c r="AR18" s="3" t="inlineStr">
+        <is>
+          <t>煤炭</t>
+        </is>
+      </c>
+      <c r="AS18" s="3" t="inlineStr">
+        <is>
+          <t>其他煤炭</t>
+        </is>
+      </c>
+      <c r="AT18" s="3" t="inlineStr">
+        <is>
+          <t>煤炭开采</t>
+        </is>
+      </c>
+      <c r="AU18" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN18" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO18" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP18" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ18" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR18" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS18" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT18" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU18" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV18" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4338,12 +4352,12 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY18" s="3" t="inlineStr">
@@ -4356,59 +4370,59 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>26东北电力SCP004</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>102683536.IB</t>
+          <t>012682210.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>10.0</v>
+        <v>5.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.98</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.98</v>
+        <v>1.51</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>57.86</v>
+        <v>31.83</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN014</t>
+          <t>26东北电力SCP003</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>235D</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>2.0055</t>
+          <t>1.5483</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
@@ -4418,12 +4432,12 @@
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>国家电投集团东北电力有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>B- 39.05</t>
+          <t>C- 10.43</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4443,21 +4457,21 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>0.43</v>
+        <v>4.18</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>5</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.55%~1.59%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4468,28 +4482,28 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务[26东北电力SCP001]</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4499,7 +4513,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
+          <t>国家电投集团东北电力有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4509,82 +4523,82 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="AK19" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AM19" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AN19" s="3" t="inlineStr">
+        <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="AM19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN19" s="3" t="inlineStr">
+      <c r="AO19" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP19" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ19" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR19" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS19" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT19" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU19" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV19" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW19" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX19" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY19" s="3" t="inlineStr">
         <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO19" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP19" s="3" t="inlineStr">
-        <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ19" s="3" t="inlineStr">
-        <is>
-          <t>化石能源</t>
-        </is>
-      </c>
-      <c r="AR19" s="3" t="inlineStr">
-        <is>
-          <t>煤炭</t>
-        </is>
-      </c>
-      <c r="AS19" s="3" t="inlineStr">
-        <is>
-          <t>其他煤炭</t>
-        </is>
-      </c>
-      <c r="AT19" s="3" t="inlineStr">
-        <is>
-          <t>煤炭开采</t>
-        </is>
-      </c>
-      <c r="AU19" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV19" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW19" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX19" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY19" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AZ19" s="3"/>

--- a/data/credit_bond_all_2026-09-04.xlsx
+++ b/data/credit_bond_all_2026-09-04.xlsx
@@ -6,7 +6,7 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="一级发行-信用债发行 2026-09-09" r:id="rId3" sheetId="1"/>
+    <sheet name="一级发行-信用债发行 2026-09-10" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
@@ -173,257 +173,257 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AV1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AW1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AX1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AY1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
       <c r="AZ1" s="1" t="inlineStr">
         <is>
-          <t>数据来源：DM    2026-09-09</t>
+          <t>数据来源：DM    2026-09-10</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="P3" s="3" t="inlineStr">
         <is>
-          <t>C+ 33.25</t>
+          <t>C 29.93</t>
         </is>
       </c>
       <c r="Q3" s="3" t="inlineStr">
@@ -1457,7 +1457,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t>C 29.95</t>
+          <t>C 26.59</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
@@ -1683,7 +1683,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t>S 90.39</t>
+          <t>S- 89.79</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
@@ -2465,7 +2465,7 @@
       <c r="AK10" s="3"/>
       <c r="AL10" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM10" s="3" t="inlineStr">
@@ -2605,7 +2605,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t>C- 20.88</t>
+          <t>C- 16.18</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t>C+ 30.82</t>
+          <t>C+ 31.04</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
@@ -2929,7 +2929,7 @@
       <c r="AK12" s="3"/>
       <c r="AL12" s="3" t="inlineStr">
         <is>
-          <t/>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM12" s="3" t="inlineStr">
@@ -2990,59 +2990,59 @@
     <row r="13" customHeight="true" ht="18.0">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>26淳安02</t>
+          <t>26东北电力SCP004</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-07 18:00</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>283908.SH</t>
+          <t>012682210.IB</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>6.5</v>
+        <v>5.0</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>6.5</v>
+        <v>5.0</v>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.50</t>
+          <t>1.30 ~ 1.80</t>
         </is>
       </c>
       <c r="H13" s="4" t="n">
-        <v>2.07</v>
+        <v>1.51</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>66.86</v>
+        <v>31.83</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>26淳安01</t>
+          <t>26东北电力SCP003</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>4.59Y</t>
+          <t>235D</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>1.9466</t>
+          <t>1.5483</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
@@ -3052,12 +3052,12 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司</t>
+          <t>国家电投集团东北电力有限公司</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t>D+ 8.10</t>
+          <t>C- 15.00</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
@@ -3067,7 +3067,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
@@ -3077,79 +3077,83 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="U13" s="4" t="n">
-        <v>2.6769</v>
+        <v>4.18</v>
       </c>
       <c r="V13" s="3"/>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
-        </is>
-      </c>
-      <c r="X13" s="3"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X13" s="3" t="inlineStr">
+        <is>
+          <t>1.55%~1.59%</t>
+        </is>
+      </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t>AA+</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z13" s="3"/>
       <c r="AA13" s="3" t="inlineStr">
         <is>
-          <t>浙江省-杭州市</t>
+          <t>辽宁省-沈阳市</t>
         </is>
       </c>
       <c r="AB13" s="3" t="inlineStr">
         <is>
-          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
+          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务[26东北电力SCP001]</t>
         </is>
       </c>
       <c r="AC13" s="3" t="inlineStr">
         <is>
-          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
+          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
         </is>
       </c>
       <c r="AD13" s="3"/>
       <c r="AE13" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF13" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG13" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH13" s="3" t="inlineStr">
         <is>
-          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
+          <t>国家电投集团东北电力有限公司2026年度第四期超短期融资券</t>
         </is>
       </c>
       <c r="AI13" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ13" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
+          <t>2027-06-05</t>
         </is>
       </c>
       <c r="AK13" s="3" t="inlineStr">
         <is>
-          <t>休1</t>
+          <t>休2</t>
         </is>
       </c>
       <c r="AL13" s="3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="AM13" s="3" t="inlineStr">
@@ -3159,50 +3163,62 @@
       </c>
       <c r="AN13" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AO13" s="3" t="inlineStr">
+        <is>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP13" s="3" t="inlineStr">
+        <is>
+          <t>4.5</t>
+        </is>
+      </c>
+      <c r="AQ13" s="3" t="inlineStr">
+        <is>
+          <t>公用事业</t>
+        </is>
+      </c>
+      <c r="AR13" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AS13" s="3" t="inlineStr">
+        <is>
+          <t>其他电力</t>
+        </is>
+      </c>
+      <c r="AT13" s="3" t="inlineStr">
+        <is>
+          <t>电力</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="AV13" s="3" t="inlineStr">
+        <is>
+          <t>无担保</t>
+        </is>
+      </c>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>不含权</t>
+        </is>
+      </c>
+      <c r="AX13" s="3" t="inlineStr">
+        <is>
+          <t>普通债权</t>
+        </is>
+      </c>
+      <c r="AY13" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO13" s="3" t="inlineStr">
-        <is>
-          <t>城投</t>
-        </is>
-      </c>
-      <c r="AP13" s="3" t="inlineStr">
-        <is>
-          <t>6.5</t>
-        </is>
-      </c>
-      <c r="AQ13" s="3"/>
-      <c r="AR13" s="3"/>
-      <c r="AS13" s="3"/>
-      <c r="AT13" s="3" t="inlineStr">
-        <is>
-          <t>综合</t>
-        </is>
-      </c>
-      <c r="AU13" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
-      <c r="AV13" s="3" t="inlineStr">
-        <is>
-          <t>无担保</t>
-        </is>
-      </c>
-      <c r="AW13" s="3" t="inlineStr">
-        <is>
-          <t>不含权</t>
-        </is>
-      </c>
-      <c r="AX13" s="3" t="inlineStr">
-        <is>
-          <t>普通债权</t>
-        </is>
-      </c>
-      <c r="AY13" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AZ13" s="3"/>
@@ -3210,74 +3226,74 @@
     <row r="14" customHeight="true" ht="18.0">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP002</t>
+          <t>26淳安02</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>012682209.IB</t>
+          <t>283908.SH</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4.0</v>
+        <v>6.5</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>4.0</v>
+        <v>6.5</v>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>1.35 ~ 1.55</t>
+          <t>1.50 ~ 2.50</t>
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>1.41</v>
+        <v>2.07</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21.84</v>
+        <v>66.86</v>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>26中兵物资SCP001</t>
+          <t>26淳安01</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t>266D</t>
+          <t>4.59Y</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>1.5500</t>
+          <t>1.9466</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>--/1.4296</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司</t>
+          <t>淳安县国有资产投资集团有限公司</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t>B- 40.00</t>
+          <t>D+ 8.10</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
@@ -3287,7 +3303,7 @@
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -3301,75 +3317,75 @@
         </is>
       </c>
       <c r="U14" s="4" t="n">
-        <v>2.575</v>
+        <v>2.6769</v>
       </c>
       <c r="V14" s="3"/>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t>5-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t>1.40%~1.44%</t>
-        </is>
-      </c>
+          <t>6+</t>
+        </is>
+      </c>
+      <c r="X14" s="3"/>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA+</t>
         </is>
       </c>
       <c r="Z14" s="3"/>
       <c r="AA14" s="3" t="inlineStr">
         <is>
-          <t>北京市</t>
+          <t>浙江省-杭州市</t>
         </is>
       </c>
       <c r="AB14" s="3" t="inlineStr">
         <is>
-          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金。</t>
+          <t>本期债券拟募集资金不超过6.5亿元(含6.5亿元),扣除发行费用后,全部用于偿还到期公司债券“23淳安02”本金。</t>
         </is>
       </c>
       <c r="AC14" s="3" t="inlineStr">
         <is>
-          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+          <t>浙商证券股份有限公司,财通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD14" s="3"/>
       <c r="AE14" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF14" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG14" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH14" s="3" t="inlineStr">
         <is>
-          <t>中国兵工物资集团有限公司2026年度第二期超短期融资券</t>
+          <t>淳安县国有资产投资集团有限公司2026年面向专业投资者非公开发行公司债券(第二期)</t>
         </is>
       </c>
       <c r="AI14" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ14" s="3" t="inlineStr">
         <is>
-          <t>2027-06-04</t>
-        </is>
-      </c>
-      <c r="AK14" s="3"/>
+          <t>2031-09-07</t>
+        </is>
+      </c>
+      <c r="AK14" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AM14" s="3" t="inlineStr">
@@ -3384,32 +3400,20 @@
       </c>
       <c r="AO14" s="3" t="inlineStr">
         <is>
-          <t>产业</t>
+          <t>城投</t>
         </is>
       </c>
       <c r="AP14" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
-        </is>
-      </c>
-      <c r="AQ14" s="3" t="inlineStr">
-        <is>
-          <t>贸易零售</t>
-        </is>
-      </c>
-      <c r="AR14" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
-      <c r="AS14" s="3" t="inlineStr">
-        <is>
-          <t>其他贸易</t>
-        </is>
-      </c>
+          <t>6.5</t>
+        </is>
+      </c>
+      <c r="AQ14" s="3"/>
+      <c r="AR14" s="3"/>
+      <c r="AS14" s="3"/>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>贸易</t>
+          <t>综合</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr">
@@ -3442,7 +3446,7 @@
     <row r="15" customHeight="true" ht="18.0">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>26腾景科技MTN001(科创债)</t>
+          <t>26中兵物资SCP002</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -3452,64 +3456,64 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>102683530.IB</t>
+          <t>012682209.IB</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t>1.08Y</t>
+          <t>0.74Y</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 2.00</t>
+          <t>1.35 ~ 1.55</t>
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>2.0</v>
+        <v>1.41</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>76.34</v>
+        <v>21.84</v>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t>23咸金03</t>
+          <t>26中兵物资SCP001</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t>242D</t>
+          <t>266D</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>1.9285</t>
+          <t>1.5500</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>--/1.4296</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司</t>
+          <t>中国兵工物资集团有限公司</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t>C- 25.00</t>
+          <t>B 55.00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
@@ -3533,53 +3537,49 @@
         </is>
       </c>
       <c r="U15" s="4" t="n">
-        <v>1.0</v>
+        <v>2.575</v>
       </c>
       <c r="V15" s="3"/>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t>8+</t>
+          <t>5-</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t>1.72%~1.82%</t>
+          <t>1.40%~1.44%</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>AA</t>
+          <t>AAA</t>
         </is>
       </c>
       <c r="Z15" s="3"/>
       <c r="AA15" s="3" t="inlineStr">
         <is>
-          <t>福建省-福州市</t>
+          <t>北京市</t>
         </is>
       </c>
       <c r="AB15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
+          <t>本期债务融资工具发行金额4亿元,募集资金拟用于偿还到期债务及补充流动资金。</t>
         </is>
       </c>
       <c r="AC15" s="3" t="inlineStr">
         <is>
-          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD15" s="3" t="inlineStr">
-        <is>
-          <t>福建省融资担保有限责任公司</t>
-        </is>
-      </c>
+          <t>中国民生银行股份有限公司,中信银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD15" s="3"/>
       <c r="AE15" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>超短期融资券(SCP)</t>
         </is>
       </c>
       <c r="AF15" s="3" t="inlineStr">
         <is>
-          <t>民营企业</t>
+          <t>国有企业</t>
         </is>
       </c>
       <c r="AG15" s="3" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="AH15" s="3" t="inlineStr">
         <is>
-          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
+          <t>中国兵工物资集团有限公司2026年度第二期超短期融资券</t>
         </is>
       </c>
       <c r="AI15" s="3" t="inlineStr">
@@ -3599,14 +3599,10 @@
       </c>
       <c r="AJ15" s="3" t="inlineStr">
         <is>
-          <t>2027-10-07</t>
-        </is>
-      </c>
-      <c r="AK15" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2027-06-04</t>
+        </is>
+      </c>
+      <c r="AK15" s="3"/>
       <c r="AL15" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -3614,7 +3610,7 @@
       </c>
       <c r="AM15" s="3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AN15" s="3" t="inlineStr">
@@ -3627,25 +3623,29 @@
           <t>产业</t>
         </is>
       </c>
-      <c r="AP15" s="3"/>
+      <c r="AP15" s="3" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
       <c r="AQ15" s="3" t="inlineStr">
         <is>
-          <t>电子制造</t>
+          <t>贸易零售</t>
         </is>
       </c>
       <c r="AR15" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>电子元器件</t>
+          <t>其他贸易</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>光学光电子</t>
+          <t>贸易</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="AV15" s="3" t="inlineStr">
         <is>
-          <t>有担保</t>
+          <t>无担保</t>
         </is>
       </c>
       <c r="AW15" s="3" t="inlineStr">
@@ -3673,77 +3673,79 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ15" s="4" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="AZ15" s="3"/>
     </row>
     <row r="16" customHeight="true" ht="18.0">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP007</t>
+          <t>26腾景科技MTN001(科创债)</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>09-04 17:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t>072610176.IB</t>
+          <t>102683530.IB</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>0.64Y</t>
+          <t>1.08Y</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>40.0</v>
+        <v>1.0</v>
       </c>
       <c r="F16" s="4" t="n">
-        <v>40.0</v>
-      </c>
-      <c r="G16" s="3"/>
+        <v>1.0</v>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>1.50 ~ 2.00</t>
+        </is>
+      </c>
       <c r="H16" s="4" t="n">
-        <v>1.5</v>
+        <v>2.0</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>28.27</v>
+        <v>76.34</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>1.47</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>26国泰海通CP003</t>
+          <t>23咸金03</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t>217D</t>
+          <t>242D</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>1.4741</t>
+          <t>1.9285</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t>1.5000/1.4600</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
+          <t>腾景科技股份有限公司</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t>A- 61.93</t>
+          <t>C 30.00</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
@@ -3766,44 +3768,54 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U16" s="3"/>
+      <c r="U16" s="4" t="n">
+        <v>1.0</v>
+      </c>
       <c r="V16" s="3"/>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8+</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t>1.47%~1.51%</t>
+          <t>1.72%~1.82%</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t>AAA</t>
+          <t>AA</t>
         </is>
       </c>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3" t="inlineStr">
         <is>
-          <t>上海市</t>
-        </is>
-      </c>
-      <c r="AB16" s="3"/>
+          <t>福建省-福州市</t>
+        </is>
+      </c>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">本次科技创新债券募集资金扣除承销费及担保费等费用后，拟全部用于发行人及其下属子公司购买光电、光学领域相关设备与原材料。 </t>
+        </is>
+      </c>
       <c r="AC16" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司</t>
-        </is>
-      </c>
-      <c r="AD16" s="3"/>
+          <t>中国建设银行股份有限公司,兴业证券股份有限公司,兴业银行股份有限公司</t>
+        </is>
+      </c>
+      <c r="AD16" s="3" t="inlineStr">
+        <is>
+          <t>福建省融资担保有限责任公司</t>
+        </is>
+      </c>
       <c r="AE16" s="3" t="inlineStr">
         <is>
-          <t>证券公司短期融资券</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF16" s="3" t="inlineStr">
         <is>
-          <t>地方国有企业</t>
+          <t>民营企业</t>
         </is>
       </c>
       <c r="AG16" s="3" t="inlineStr">
@@ -3813,7 +3825,7 @@
       </c>
       <c r="AH16" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
+          <t>腾景科技股份有限公司2026年度第一期科技创新债券</t>
         </is>
       </c>
       <c r="AI16" s="3" t="inlineStr">
@@ -3823,10 +3835,14 @@
       </c>
       <c r="AJ16" s="3" t="inlineStr">
         <is>
-          <t>2027-04-28</t>
-        </is>
-      </c>
-      <c r="AK16" s="3"/>
+          <t>2027-10-07</t>
+        </is>
+      </c>
+      <c r="AK16" s="3" t="inlineStr">
+        <is>
+          <t>休1</t>
+        </is>
+      </c>
       <c r="AL16" s="3" t="inlineStr">
         <is>
           <t>2026-09-08</t>
@@ -3834,42 +3850,38 @@
       </c>
       <c r="AM16" s="3" t="inlineStr">
         <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AN16" s="3" t="inlineStr">
+        <is>
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="AN16" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
       <c r="AO16" s="3" t="inlineStr">
         <is>
-          <t>金融</t>
-        </is>
-      </c>
-      <c r="AP16" s="3" t="inlineStr">
-        <is>
-          <t>2.5</t>
-        </is>
-      </c>
+          <t>产业</t>
+        </is>
+      </c>
+      <c r="AP16" s="3"/>
       <c r="AQ16" s="3" t="inlineStr">
         <is>
-          <t>非银</t>
+          <t>电子制造</t>
         </is>
       </c>
       <c r="AR16" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>券商</t>
+          <t>电子元器件</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>证券</t>
+          <t>光学光电子</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr">
@@ -3879,7 +3891,7 @@
       </c>
       <c r="AV16" s="3" t="inlineStr">
         <is>
-          <t>无担保</t>
+          <t>有担保</t>
         </is>
       </c>
       <c r="AW16" s="3" t="inlineStr">
@@ -3897,79 +3909,77 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="AZ16" s="3"/>
+      <c r="AZ16" s="4" t="n">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="17" customHeight="true" ht="18.0">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y7</t>
+          <t>26国泰海通CP007</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>09-04 19:00</t>
+          <t>09-04 17:00</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t>283876.SH</t>
+          <t>072610176.IB</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>3+N</t>
+          <t>0.64Y</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>9.0</v>
+        <v>40.0</v>
       </c>
       <c r="F17" s="4" t="n">
-        <v>9.0</v>
-      </c>
-      <c r="G17" s="3" t="inlineStr">
-        <is>
-          <t>1.70 ~ 2.30</t>
-        </is>
-      </c>
+        <v>40.0</v>
+      </c>
+      <c r="G17" s="3"/>
       <c r="H17" s="4" t="n">
-        <v>1.99</v>
+        <v>1.5</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>74.22</v>
+        <v>28.27</v>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.47</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>26山钢Y6</t>
+          <t>26国泰海通CP003</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t>2.96Y+N</t>
+          <t>217D</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>2.0599</t>
+          <t>1.4741</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>1.5000/1.4600</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t>B- 36.65</t>
+          <t>A- 64.25</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
@@ -3979,7 +3989,7 @@
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t>09-04 15:00</t>
+          <t>09-04 09:00</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
@@ -3992,18 +4002,16 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="U17" s="4" t="n">
-        <v>3.58</v>
-      </c>
+      <c r="U17" s="3"/>
       <c r="V17" s="3"/>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>6+</t>
+          <t>2</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t>1.92%~2.02%</t>
+          <t>1.47%~1.51%</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
@@ -4014,23 +4022,19 @@
       <c r="Z17" s="3"/>
       <c r="AA17" s="3" t="inlineStr">
         <is>
-          <t>山东省-济南市</t>
-        </is>
-      </c>
-      <c r="AB17" s="3" t="inlineStr">
-        <is>
-          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
-        </is>
-      </c>
+          <t>上海市</t>
+        </is>
+      </c>
+      <c r="AB17" s="3"/>
       <c r="AC17" s="3" t="inlineStr">
         <is>
-          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司</t>
         </is>
       </c>
       <c r="AD17" s="3"/>
       <c r="AE17" s="3" t="inlineStr">
         <is>
-          <t>公司债券</t>
+          <t>证券公司短期融资券</t>
         </is>
       </c>
       <c r="AF17" s="3" t="inlineStr">
@@ -4040,75 +4044,75 @@
       </c>
       <c r="AG17" s="3" t="inlineStr">
         <is>
-          <t>上交所</t>
+          <t>银行间</t>
         </is>
       </c>
       <c r="AH17" s="3" t="inlineStr">
         <is>
-          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
+          <t>国泰海通证券股份有限公司2026年度第七期短期融资券</t>
         </is>
       </c>
       <c r="AI17" s="3" t="inlineStr">
         <is>
-          <t>私募</t>
+          <t>公募</t>
         </is>
       </c>
       <c r="AJ17" s="3" t="inlineStr">
         <is>
-          <t>2029-09-07</t>
+          <t>2027-04-28</t>
         </is>
       </c>
       <c r="AK17" s="3"/>
       <c r="AL17" s="3" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="AM17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AN17" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AO17" s="3" t="inlineStr">
+        <is>
+          <t>金融</t>
+        </is>
+      </c>
+      <c r="AP17" s="3" t="inlineStr">
+        <is>
+          <t>2.5</t>
+        </is>
+      </c>
+      <c r="AQ17" s="3" t="inlineStr">
+        <is>
+          <t>非银</t>
+        </is>
+      </c>
+      <c r="AR17" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AS17" s="3" t="inlineStr">
+        <is>
+          <t>券商</t>
+        </is>
+      </c>
+      <c r="AT17" s="3" t="inlineStr">
+        <is>
+          <t>证券</t>
+        </is>
+      </c>
+      <c r="AU17" s="3" t="inlineStr">
+        <is>
           <t/>
         </is>
       </c>
-      <c r="AM17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-03</t>
-        </is>
-      </c>
-      <c r="AN17" s="3" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="AO17" s="3" t="inlineStr">
-        <is>
-          <t>产业</t>
-        </is>
-      </c>
-      <c r="AP17" s="3" t="inlineStr">
-        <is>
-          <t>4.5</t>
-        </is>
-      </c>
-      <c r="AQ17" s="3" t="inlineStr">
-        <is>
-          <t>金属和非金属矿产</t>
-        </is>
-      </c>
-      <c r="AR17" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AS17" s="3" t="inlineStr">
-        <is>
-          <t>普钢</t>
-        </is>
-      </c>
-      <c r="AT17" s="3" t="inlineStr">
-        <is>
-          <t>钢铁</t>
-        </is>
-      </c>
-      <c r="AU17" s="3" t="inlineStr">
-        <is>
-          <t/>
-        </is>
-      </c>
       <c r="AV17" s="3" t="inlineStr">
         <is>
           <t>无担保</t>
@@ -4116,12 +4120,12 @@
       </c>
       <c r="AW17" s="3" t="inlineStr">
         <is>
-          <t>永续</t>
+          <t>不含权</t>
         </is>
       </c>
       <c r="AX17" s="3" t="inlineStr">
         <is>
-          <t>次级债权</t>
+          <t>普通债权</t>
         </is>
       </c>
       <c r="AY17" s="3" t="inlineStr">
@@ -4134,74 +4138,74 @@
     <row r="18" customHeight="true" ht="18.0">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN016</t>
+          <t>26山钢Y7</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>09-04 18:00</t>
+          <t>09-04 19:00</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>102683536.IB</t>
+          <t>283876.SH</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>5Y</t>
+          <t>3+N</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>10.0</v>
+        <v>9.0</v>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>1.50 ~ 1.98</t>
+          <t>1.70 ~ 2.30</t>
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>57.86</v>
+        <v>74.22</v>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>26晋能煤业MTN014</t>
+          <t>26山钢Y6</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t>4.94Y</t>
+          <t>2.96Y+N</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>2.0055</t>
+          <t>2.0599</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t>2.0000/1.9900</t>
+          <t>--/--</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司</t>
+          <t>山东钢铁集团有限公司</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t>B- 36.34</t>
+          <t>B- 35.93</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
@@ -4211,7 +4215,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t>09-04 09:00</t>
+          <t>09-04 15:00</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
@@ -4225,12 +4229,12 @@
         </is>
       </c>
       <c r="U18" s="4" t="n">
-        <v>0.43</v>
+        <v>3.58</v>
       </c>
       <c r="V18" s="3"/>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t>6-</t>
+          <t>6+</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
@@ -4246,23 +4250,23 @@
       <c r="Z18" s="3"/>
       <c r="AA18" s="3" t="inlineStr">
         <is>
-          <t>山西省-大同市</t>
+          <t>山东省-济南市</t>
         </is>
       </c>
       <c r="AB18" s="3" t="inlineStr">
         <is>
-          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
+          <t>本期债券的募集资金在扣除发行费用后,拟将用于置换到期的公司债券本金。[24山钢Y3]</t>
         </is>
       </c>
       <c r="AC18" s="3" t="inlineStr">
         <is>
-          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
+          <t>国泰海通证券股份有限公司,中信建投证券股份有限公司,中信证券股份有限公司,中国国际金融股份有限公司,华泰联合证券有限责任公司,招商证券股份有限公司</t>
         </is>
       </c>
       <c r="AD18" s="3"/>
       <c r="AE18" s="3" t="inlineStr">
         <is>
-          <t>中期票据</t>
+          <t>公司债券</t>
         </is>
       </c>
       <c r="AF18" s="3" t="inlineStr">
@@ -4272,32 +4276,28 @@
       </c>
       <c r="AG18" s="3" t="inlineStr">
         <is>
-          <t>银行间</t>
+          <t>上交所</t>
         </is>
       </c>
       <c r="AH18" s="3" t="inlineStr">
         <is>
-          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
+          <t>山东钢铁集团有限公司2026年面向专业投资者非公开发行可续期公司债券(第五期)</t>
         </is>
       </c>
       <c r="AI18" s="3" t="inlineStr">
         <is>
-          <t>公募</t>
+          <t>私募</t>
         </is>
       </c>
       <c r="AJ18" s="3" t="inlineStr">
         <is>
-          <t>2031-09-07</t>
-        </is>
-      </c>
-      <c r="AK18" s="3" t="inlineStr">
-        <is>
-          <t>休1</t>
-        </is>
-      </c>
+          <t>2029-09-07</t>
+        </is>
+      </c>
+      <c r="AK18" s="3"/>
       <c r="AL18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="AM18" s="3" t="inlineStr">
@@ -4317,27 +4317,27 @@
       </c>
       <c r="AP18" s="3" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="AQ18" s="3" t="inlineStr">
         <is>
-          <t>化石能源</t>
+          <t>金属和非金属矿产</t>
         </is>
       </c>
       <c r="AR18" s="3" t="inlineStr">
         <is>
-          <t>煤炭</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>其他煤炭</t>
+          <t>普钢</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>煤炭开采</t>
+          <t>钢铁</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="AW18" s="3" t="inlineStr">
         <is>
-          <t>不含权</t>
+          <t>永续</t>
         </is>
       </c>
       <c r="AX18" s="3" t="inlineStr">
         <is>
-          <t>普通债权</t>
+          <t>次级债权</t>
         </is>
       </c>
       <c r="AY18" s="3" t="inlineStr">
@@ -4370,74 +4370,74 @@
     <row r="19" customHeight="true" ht="18.0">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP004</t>
+          <t>26晋能煤业MTN016</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>09-07 18:00</t>
+          <t>09-04 18:00</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>012682210.IB</t>
+          <t>102683536.IB</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>0.74Y</t>
+          <t>5Y</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>1.30 ~ 1.80</t>
+          <t>1.50 ~ 1.98</t>
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>1.51</v>
+        <v>1.98</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>31.83</v>
+        <v>57.86</v>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>26东北电力SCP003</t>
+          <t>26晋能煤业MTN014</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t>235D</t>
+          <t>4.94Y</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>1.5483</t>
+          <t>2.0055</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t>--/--</t>
+          <t>2.0000/1.9900</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司</t>
+          <t>晋能控股煤业集团有限公司</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t>C- 10.43</t>
+          <t>B- 35.79</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
@@ -4457,21 +4457,21 @@
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="U19" s="4" t="n">
-        <v>4.18</v>
+        <v>0.43</v>
       </c>
       <c r="V19" s="3"/>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6-</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>1.55%~1.59%</t>
+          <t>1.92%~2.02%</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
@@ -4482,28 +4482,28 @@
       <c r="Z19" s="3"/>
       <c r="AA19" s="3" t="inlineStr">
         <is>
-          <t>辽宁省-沈阳市</t>
+          <t>山西省-大同市</t>
         </is>
       </c>
       <c r="AB19" s="3" t="inlineStr">
         <is>
-          <t>本期超短期融资券发行规模为人民币5.00亿元,本次债券募集资金拟用于偿还发行人本部及合并范围内子公司有息债务[26东北电力SCP001]</t>
+          <t>发行人本期中期票据基础发行规模0亿元，发行金额上限10亿元，募集资金拟用于偿还发行人及下属子公司的有息负债。</t>
         </is>
       </c>
       <c r="AC19" s="3" t="inlineStr">
         <is>
-          <t>招商银行股份有限公司,中国工商银行股份有限公司</t>
+          <t>上海浦东发展银行股份有限公司,国投证券股份有限公司</t>
         </is>
       </c>
       <c r="AD19" s="3"/>
       <c r="AE19" s="3" t="inlineStr">
         <is>
-          <t>超短期融资券(SCP)</t>
+          <t>中期票据</t>
         </is>
       </c>
       <c r="AF19" s="3" t="inlineStr">
         <is>
-          <t>国有企业</t>
+          <t>地方国有企业</t>
         </is>
       </c>
       <c r="AG19" s="3" t="inlineStr">
@@ -4513,7 +4513,7 @@
       </c>
       <c r="AH19" s="3" t="inlineStr">
         <is>
-          <t>国家电投集团东北电力有限公司2026年度第四期超短期融资券</t>
+          <t>晋能控股煤业集团有限公司2026年度第十六期中期票据</t>
         </is>
       </c>
       <c r="AI19" s="3" t="inlineStr">
@@ -4523,17 +4523,17 @@
       </c>
       <c r="AJ19" s="3" t="inlineStr">
         <is>
-          <t>2027-06-05</t>
+          <t>2031-09-07</t>
         </is>
       </c>
       <c r="AK19" s="3" t="inlineStr">
         <is>
-          <t>休2</t>
+          <t>休1</t>
         </is>
       </c>
       <c r="AL19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="AM19" s="3" t="inlineStr">
@@ -4543,7 +4543,7 @@
       </c>
       <c r="AN19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="AO19" s="3" t="inlineStr">
@@ -4553,27 +4553,27 @@
       </c>
       <c r="AP19" s="3" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="AQ19" s="3" t="inlineStr">
         <is>
-          <t>公用事业</t>
+          <t>化石能源</t>
         </is>
       </c>
       <c r="AR19" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤炭</t>
         </is>
       </c>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>其他电力</t>
+          <t>其他煤炭</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>电力</t>
+          <t>煤炭开采</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AY19" s="3" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AZ19" s="3"/>
